--- a/data/data_minerals/USGS/Mineral_yearbook/myb1-2023-cobal-ERT.xlsx
+++ b/data/data_minerals/USGS/Mineral_yearbook/myb1-2023-cobal-ERT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca0-my.sharepoint.com/personal/marin_pellan_polymtlus_ca/Documents/Desktop/POST_DOC/Project/plca_metals_github/plca_metals/data/data_minerals/USGS/Mineral_yearbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE9CC3C-8250-4489-8823-3CD66631908B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{DCE9CC3C-8250-4489-8823-3CD66631908B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F8114EE-A105-4052-B84C-0F26032DAF97}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="12" r:id="rId1"/>
@@ -2191,7 +2191,7 @@
   </si>
   <si>
     <r>
-      <t>2</t>
+      <t>3</t>
     </r>
     <r>
       <rPr>
@@ -2200,24 +2200,279 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>Figures represent recoverable cobalt content from ores, concentrates, or intermediate products from cobalt, copper, nickel, platinum, or zinc operations.</t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <t>Other copper-, iron (pyrite)-, nickel-, platinum-, or zinc-producing countries and (or) localities also may have produced ores containing cobalt as a byproduct component, but recovery was small or zero.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Cobalt content of lateritic nickel ore and nickel concentrate reported by the government of Western Australia.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Recoverable cobalt in concentrates shipped reported by Statistics Canada. Data prior to 2019 are mineral production reported by Natural Resources Canada.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Determined from reported or estimated cobalt content of materials originating from mining and processing operations in Congo (Kinshasa) such as ores, concentrates, refined cobalt metal, and intermediate products including crude cobalt alloys, crude cobalt hydroxide, and crude cobalt carbonate produced from cobalt ores and concentrates, tailings, or slags.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Determined from estimated cobalt content of nickel-cobalt sulfide production and estimated cobalt content of ammoniacal liquor production.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Determined from estimated cobalt content of nickel matte plus estimated cobalt content of nickel-cobalt hydroxide.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Estimated cobalt content of ore production based on reported or estimated cobalt metal powder production and nickel recovery rates.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Cobalt content of concentrate estimated from reported or estimated gross weight.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Cobalt content of nickel hydroxide. Data prior to 2021 include cobalt content of cobalt carbonate.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Cobalt content of nickel-cobalt hydroxide.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Cobalt content of nickel-cobalt sulfide.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Cobalt content of concentrates.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Cobalt content of cobalt carbonate and nickel-cobalt hydroxide.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Table includes data available through October 1, 2024. Data are rounded to no more than three significant digits, except prices.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
       <t>3</t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Other copper-, iron (pyrite)-, nickel-, platinum-, or zinc-producing countries and (or) localities also may have produced ores containing cobalt as a byproduct component, but recovery was small or zero.</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>For 2019-2021, defined as imports minus exports plus adjustments for Government and industry stock changes plus secondary production, as estimated from consumption of purchased scrap. Beginning in 2022, Government stocks no longer included.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Metal</t>
+    </r>
     <r>
       <rPr>
         <vertAlign val="superscript"/>
@@ -2225,18 +2480,13 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Cobalt content of lateritic nickel ore and nickel concentrate reported by the government of Western Australia.</t>
-    </r>
-  </si>
-  <si>
+      <t>6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>U.S. exports of cobalt:</t>
+    </r>
     <r>
       <rPr>
         <vertAlign val="superscript"/>
@@ -2244,15 +2494,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Recoverable cobalt in concentrates shipped reported by Statistics Canada. Data prior to 2019 are mineral production reported by Natural Resources Canada.</t>
+      <t>7</t>
     </r>
   </si>
   <si>
@@ -2271,7 +2513,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>Determined from reported or estimated cobalt content of materials originating from mining and processing operations in Congo (Kinshasa) such as ores, concentrates, refined cobalt metal, and intermediate products including crude cobalt alloys, crude cobalt hydroxide, and crude cobalt carbonate produced from cobalt ores and concentrates, tailings, or slags.</t>
+      <t>Unwrought cobalt, excluding alloys and waste and scrap.</t>
     </r>
   </si>
   <si>
@@ -2290,10 +2532,19 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>Determined from estimated cobalt content of nickel-cobalt sulfide production and estimated cobalt content of ammoniacal liquor production.</t>
-    </r>
-  </si>
-  <si>
+      <t>In addition to the materials listed, the United States exported cobalt ores and concentrates and wrought cobalt and cobalt articles.</t>
+    </r>
+  </si>
+  <si>
+    <t>r, e, 3</t>
+  </si>
+  <si>
+    <t>e, 3</t>
+  </si>
+  <si>
+    <r>
+      <t>Industry</t>
+    </r>
     <r>
       <rPr>
         <vertAlign val="superscript"/>
@@ -2301,271 +2552,6 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Determined from estimated cobalt content of nickel matte plus estimated cobalt content of nickel-cobalt hydroxide.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Estimated cobalt content of ore production based on reported or estimated cobalt metal powder production and nickel recovery rates.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Cobalt content of concentrate estimated from reported or estimated gross weight.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Cobalt content of nickel hydroxide. Data prior to 2021 include cobalt content of cobalt carbonate.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Cobalt content of nickel-cobalt hydroxide.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>13</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Cobalt content of nickel-cobalt sulfide.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Cobalt content of concentrates.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Cobalt content of cobalt carbonate and nickel-cobalt hydroxide.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Table includes data available through October 1, 2024. Data are rounded to no more than three significant digits, except prices.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>For 2019-2021, defined as imports minus exports plus adjustments for Government and industry stock changes plus secondary production, as estimated from consumption of purchased scrap. Beginning in 2022, Government stocks no longer included.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Metal</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>6</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>U.S. exports of cobalt:</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>7</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Unwrought cobalt, excluding alloys and waste and scrap.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>In addition to the materials listed, the United States exported cobalt ores and concentrates and wrought cobalt and cobalt articles.</t>
-    </r>
-  </si>
-  <si>
-    <t>r, e, 3</t>
-  </si>
-  <si>
-    <t>e, 3</t>
-  </si>
-  <si>
-    <r>
-      <t>Industry</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
       <t>e, 2, 4</t>
     </r>
   </si>
@@ -2592,6 +2578,9 @@
   </si>
   <si>
     <t>Posted:  February 6, 2025</t>
+  </si>
+  <si>
+    <t>total</t>
   </si>
 </sst>
 </file>
@@ -3977,6 +3966,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3988,16 +3985,12 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4009,7 +4002,15 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -4025,16 +4026,8 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4049,10 +4042,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4060,6 +4049,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -4082,9 +4074,6 @@
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4463,7 +4452,7 @@
     <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A5" s="209" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B5" s="210"/>
       <c r="C5" s="210"/>
@@ -4479,7 +4468,7 @@
     </row>
     <row r="6" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A6" s="212" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B6" s="213"/>
       <c r="C6" s="213"/>
@@ -4495,7 +4484,7 @@
     </row>
     <row r="7" spans="1:12" s="199" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
       <c r="A7" s="203" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -4511,7 +4500,7 @@
     </row>
     <row r="8" spans="1:12" s="199" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
       <c r="A8" s="203" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B8" s="204"/>
       <c r="C8" s="204"/>
@@ -4527,7 +4516,7 @@
     </row>
     <row r="9" spans="1:12" s="199" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
       <c r="A9" s="203" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B9" s="204"/>
       <c r="C9" s="204"/>
@@ -4543,7 +4532,7 @@
     </row>
     <row r="10" spans="1:12" s="199" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
       <c r="A10" s="203" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B10" s="204"/>
       <c r="C10" s="204"/>
@@ -4559,7 +4548,7 @@
     </row>
     <row r="11" spans="1:12" s="199" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
       <c r="A11" s="203" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B11" s="204"/>
       <c r="C11" s="204"/>
@@ -4589,7 +4578,7 @@
     </row>
     <row r="13" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="206" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B13" s="207"/>
       <c r="C13" s="207"/>
@@ -4654,80 +4643,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="218" t="s">
+      <c r="A1" s="215" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="218"/>
-      <c r="C1" s="218"/>
-      <c r="D1" s="218"/>
-      <c r="E1" s="218"/>
-      <c r="F1" s="218"/>
-      <c r="G1" s="218"/>
-      <c r="H1" s="218"/>
-      <c r="I1" s="218"/>
-      <c r="J1" s="218"/>
-      <c r="K1" s="218"/>
-      <c r="L1" s="218"/>
+      <c r="B1" s="215"/>
+      <c r="C1" s="215"/>
+      <c r="D1" s="215"/>
+      <c r="E1" s="215"/>
+      <c r="F1" s="215"/>
+      <c r="G1" s="215"/>
+      <c r="H1" s="215"/>
+      <c r="I1" s="215"/>
+      <c r="J1" s="215"/>
+      <c r="K1" s="215"/>
+      <c r="L1" s="215"/>
     </row>
     <row r="2" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="218" t="s">
+      <c r="A2" s="215" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="218"/>
-      <c r="C2" s="218"/>
-      <c r="D2" s="218"/>
-      <c r="E2" s="218"/>
-      <c r="F2" s="218"/>
-      <c r="G2" s="218"/>
-      <c r="H2" s="218"/>
-      <c r="I2" s="218"/>
-      <c r="J2" s="218"/>
-      <c r="K2" s="218"/>
-      <c r="L2" s="218"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
     </row>
     <row r="3" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="218"/>
-      <c r="B3" s="218"/>
-      <c r="C3" s="218"/>
-      <c r="D3" s="218"/>
-      <c r="E3" s="218"/>
-      <c r="F3" s="218"/>
-      <c r="G3" s="218"/>
-      <c r="H3" s="218"/>
-      <c r="I3" s="218"/>
-      <c r="J3" s="218"/>
-      <c r="K3" s="218"/>
-      <c r="L3" s="218"/>
+      <c r="A3" s="215"/>
+      <c r="B3" s="215"/>
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="215"/>
+      <c r="G3" s="215"/>
+      <c r="H3" s="215"/>
+      <c r="I3" s="215"/>
+      <c r="J3" s="215"/>
+      <c r="K3" s="215"/>
+      <c r="L3" s="215"/>
     </row>
     <row r="4" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="218" t="s">
+      <c r="A4" s="215" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="218"/>
-      <c r="C4" s="218"/>
-      <c r="D4" s="218"/>
-      <c r="E4" s="218"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="218"/>
-      <c r="H4" s="218"/>
-      <c r="I4" s="218"/>
-      <c r="J4" s="218"/>
-      <c r="K4" s="218"/>
-      <c r="L4" s="218"/>
+      <c r="B4" s="215"/>
+      <c r="C4" s="215"/>
+      <c r="D4" s="215"/>
+      <c r="E4" s="215"/>
+      <c r="F4" s="215"/>
+      <c r="G4" s="215"/>
+      <c r="H4" s="215"/>
+      <c r="I4" s="215"/>
+      <c r="J4" s="215"/>
+      <c r="K4" s="215"/>
+      <c r="L4" s="215"/>
     </row>
     <row r="5" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="219"/>
-      <c r="B5" s="219"/>
-      <c r="C5" s="219"/>
-      <c r="D5" s="219"/>
-      <c r="E5" s="219"/>
-      <c r="F5" s="219"/>
-      <c r="G5" s="219"/>
-      <c r="H5" s="219"/>
-      <c r="I5" s="219"/>
-      <c r="J5" s="219"/>
-      <c r="K5" s="219"/>
-      <c r="L5" s="219"/>
+      <c r="A5" s="216"/>
+      <c r="B5" s="216"/>
+      <c r="C5" s="216"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="216"/>
+      <c r="K5" s="216"/>
+      <c r="L5" s="216"/>
     </row>
     <row r="6" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="102"/>
@@ -4937,7 +4926,7 @@
     </row>
     <row r="15" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="47" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="1"/>
@@ -5178,148 +5167,148 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="217" t="s">
+      <c r="A25" s="219" t="s">
         <v>112</v>
       </c>
-      <c r="B25" s="217"/>
-      <c r="C25" s="217"/>
-      <c r="D25" s="217"/>
-      <c r="E25" s="217"/>
-      <c r="F25" s="217"/>
-      <c r="G25" s="217"/>
-      <c r="H25" s="217"/>
-      <c r="I25" s="217"/>
-      <c r="J25" s="217"/>
-      <c r="K25" s="217"/>
-      <c r="L25" s="217"/>
+      <c r="B25" s="219"/>
+      <c r="C25" s="219"/>
+      <c r="D25" s="219"/>
+      <c r="E25" s="219"/>
+      <c r="F25" s="219"/>
+      <c r="G25" s="219"/>
+      <c r="H25" s="219"/>
+      <c r="I25" s="219"/>
+      <c r="J25" s="219"/>
+      <c r="K25" s="219"/>
+      <c r="L25" s="219"/>
     </row>
     <row r="26" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="215" t="s">
+      <c r="A26" s="217" t="s">
+        <v>240</v>
+      </c>
+      <c r="B26" s="217"/>
+      <c r="C26" s="217"/>
+      <c r="D26" s="217"/>
+      <c r="E26" s="217"/>
+      <c r="F26" s="217"/>
+      <c r="G26" s="217"/>
+      <c r="H26" s="217"/>
+      <c r="I26" s="217"/>
+      <c r="J26" s="217"/>
+      <c r="K26" s="217"/>
+      <c r="L26" s="217"/>
+    </row>
+    <row r="27" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="217" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" s="217"/>
+      <c r="C27" s="217"/>
+      <c r="D27" s="217"/>
+      <c r="E27" s="217"/>
+      <c r="F27" s="217"/>
+      <c r="G27" s="217"/>
+      <c r="H27" s="217"/>
+      <c r="I27" s="217"/>
+      <c r="J27" s="217"/>
+      <c r="K27" s="217"/>
+      <c r="L27" s="217"/>
+    </row>
+    <row r="28" spans="1:12" s="81" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="218" t="s">
         <v>241</v>
       </c>
-      <c r="B26" s="215"/>
-      <c r="C26" s="215"/>
-      <c r="D26" s="215"/>
-      <c r="E26" s="215"/>
-      <c r="F26" s="215"/>
-      <c r="G26" s="215"/>
-      <c r="H26" s="215"/>
-      <c r="I26" s="215"/>
-      <c r="J26" s="215"/>
-      <c r="K26" s="215"/>
-      <c r="L26" s="215"/>
-    </row>
-    <row r="27" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="215" t="s">
-        <v>117</v>
-      </c>
-      <c r="B27" s="215"/>
-      <c r="C27" s="215"/>
-      <c r="D27" s="215"/>
-      <c r="E27" s="215"/>
-      <c r="F27" s="215"/>
-      <c r="G27" s="215"/>
-      <c r="H27" s="215"/>
-      <c r="I27" s="215"/>
-      <c r="J27" s="215"/>
-      <c r="K27" s="215"/>
-      <c r="L27" s="215"/>
-    </row>
-    <row r="28" spans="1:12" s="81" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="216" t="s">
-        <v>242</v>
-      </c>
-      <c r="B28" s="216"/>
-      <c r="C28" s="216"/>
-      <c r="D28" s="216"/>
-      <c r="E28" s="216"/>
-      <c r="F28" s="216"/>
-      <c r="G28" s="216"/>
-      <c r="H28" s="216"/>
-      <c r="I28" s="216"/>
-      <c r="J28" s="216"/>
-      <c r="K28" s="216"/>
-      <c r="L28" s="216"/>
+      <c r="B28" s="218"/>
+      <c r="C28" s="218"/>
+      <c r="D28" s="218"/>
+      <c r="E28" s="218"/>
+      <c r="F28" s="218"/>
+      <c r="G28" s="218"/>
+      <c r="H28" s="218"/>
+      <c r="I28" s="218"/>
+      <c r="J28" s="218"/>
+      <c r="K28" s="218"/>
+      <c r="L28" s="218"/>
     </row>
     <row r="29" spans="1:12" s="81" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="215" t="s">
+      <c r="A29" s="217" t="s">
         <v>118</v>
       </c>
-      <c r="B29" s="215"/>
-      <c r="C29" s="215"/>
-      <c r="D29" s="215"/>
-      <c r="E29" s="215"/>
-      <c r="F29" s="215"/>
-      <c r="G29" s="215"/>
-      <c r="H29" s="215"/>
-      <c r="I29" s="215"/>
-      <c r="J29" s="215"/>
-      <c r="K29" s="215"/>
-      <c r="L29" s="215"/>
+      <c r="B29" s="217"/>
+      <c r="C29" s="217"/>
+      <c r="D29" s="217"/>
+      <c r="E29" s="217"/>
+      <c r="F29" s="217"/>
+      <c r="G29" s="217"/>
+      <c r="H29" s="217"/>
+      <c r="I29" s="217"/>
+      <c r="J29" s="217"/>
+      <c r="K29" s="217"/>
+      <c r="L29" s="217"/>
     </row>
     <row r="30" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="215" t="s">
+      <c r="A30" s="217" t="s">
         <v>147</v>
       </c>
-      <c r="B30" s="215"/>
-      <c r="C30" s="215"/>
-      <c r="D30" s="215"/>
-      <c r="E30" s="215"/>
-      <c r="F30" s="215"/>
-      <c r="G30" s="215"/>
-      <c r="H30" s="215"/>
-      <c r="I30" s="215"/>
-      <c r="J30" s="215"/>
-      <c r="K30" s="215"/>
-      <c r="L30" s="215"/>
+      <c r="B30" s="217"/>
+      <c r="C30" s="217"/>
+      <c r="D30" s="217"/>
+      <c r="E30" s="217"/>
+      <c r="F30" s="217"/>
+      <c r="G30" s="217"/>
+      <c r="H30" s="217"/>
+      <c r="I30" s="217"/>
+      <c r="J30" s="217"/>
+      <c r="K30" s="217"/>
+      <c r="L30" s="217"/>
     </row>
     <row r="31" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="216" t="s">
+      <c r="A31" s="218" t="s">
         <v>200</v>
       </c>
-      <c r="B31" s="216"/>
-      <c r="C31" s="216"/>
-      <c r="D31" s="216"/>
-      <c r="E31" s="216"/>
-      <c r="F31" s="216"/>
-      <c r="G31" s="216"/>
-      <c r="H31" s="216"/>
-      <c r="I31" s="216"/>
-      <c r="J31" s="216"/>
-      <c r="K31" s="216"/>
-      <c r="L31" s="216"/>
+      <c r="B31" s="218"/>
+      <c r="C31" s="218"/>
+      <c r="D31" s="218"/>
+      <c r="E31" s="218"/>
+      <c r="F31" s="218"/>
+      <c r="G31" s="218"/>
+      <c r="H31" s="218"/>
+      <c r="I31" s="218"/>
+      <c r="J31" s="218"/>
+      <c r="K31" s="218"/>
+      <c r="L31" s="218"/>
     </row>
     <row r="32" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="216" t="s">
+      <c r="A32" s="218" t="s">
         <v>144</v>
       </c>
-      <c r="B32" s="216"/>
-      <c r="C32" s="216"/>
-      <c r="D32" s="216"/>
-      <c r="E32" s="216"/>
-      <c r="F32" s="216"/>
-      <c r="G32" s="216"/>
-      <c r="H32" s="216"/>
-      <c r="I32" s="216"/>
-      <c r="J32" s="216"/>
-      <c r="K32" s="216"/>
-      <c r="L32" s="216"/>
+      <c r="B32" s="218"/>
+      <c r="C32" s="218"/>
+      <c r="D32" s="218"/>
+      <c r="E32" s="218"/>
+      <c r="F32" s="218"/>
+      <c r="G32" s="218"/>
+      <c r="H32" s="218"/>
+      <c r="I32" s="218"/>
+      <c r="J32" s="218"/>
+      <c r="K32" s="218"/>
+      <c r="L32" s="218"/>
     </row>
     <row r="33" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="215" t="s">
+      <c r="A33" s="217" t="s">
         <v>145</v>
       </c>
-      <c r="B33" s="215"/>
-      <c r="C33" s="215"/>
-      <c r="D33" s="215"/>
-      <c r="E33" s="215"/>
-      <c r="F33" s="215"/>
-      <c r="G33" s="215"/>
-      <c r="H33" s="215"/>
-      <c r="I33" s="215"/>
-      <c r="J33" s="215"/>
-      <c r="K33" s="215"/>
-      <c r="L33" s="215"/>
+      <c r="B33" s="217"/>
+      <c r="C33" s="217"/>
+      <c r="D33" s="217"/>
+      <c r="E33" s="217"/>
+      <c r="F33" s="217"/>
+      <c r="G33" s="217"/>
+      <c r="H33" s="217"/>
+      <c r="I33" s="217"/>
+      <c r="J33" s="217"/>
+      <c r="K33" s="217"/>
+      <c r="L33" s="217"/>
     </row>
     <row r="34" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="54"/>
@@ -5337,11 +5326,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A5:L5"/>
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="A31:L31"/>
     <mergeCell ref="A33:L33"/>
@@ -5351,6 +5335,11 @@
     <mergeCell ref="A29:L29"/>
     <mergeCell ref="A27:L27"/>
     <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A5:L5"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5370,45 +5359,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="218" t="s">
+      <c r="A1" s="215" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="218"/>
-      <c r="C1" s="218"/>
-      <c r="D1" s="218"/>
-      <c r="E1" s="218"/>
+      <c r="B1" s="215"/>
+      <c r="C1" s="215"/>
+      <c r="D1" s="215"/>
+      <c r="E1" s="215"/>
     </row>
     <row r="2" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="218" t="s">
+      <c r="A2" s="215" t="s">
         <v>108</v>
       </c>
-      <c r="B2" s="218"/>
-      <c r="C2" s="218"/>
-      <c r="D2" s="218"/>
-      <c r="E2" s="218"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
     </row>
     <row r="3" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="218"/>
-      <c r="B3" s="218"/>
-      <c r="C3" s="218"/>
-      <c r="D3" s="218"/>
-      <c r="E3" s="218"/>
+      <c r="A3" s="215"/>
+      <c r="B3" s="215"/>
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
     </row>
     <row r="4" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="218" t="s">
+      <c r="A4" s="215" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="218"/>
-      <c r="C4" s="218"/>
-      <c r="D4" s="218"/>
-      <c r="E4" s="218"/>
+      <c r="B4" s="215"/>
+      <c r="C4" s="215"/>
+      <c r="D4" s="215"/>
+      <c r="E4" s="215"/>
     </row>
     <row r="5" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="218"/>
-      <c r="B5" s="218"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="218"/>
-      <c r="E5" s="218"/>
+      <c r="A5" s="215"/>
+      <c r="B5" s="215"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="215"/>
+      <c r="E5" s="215"/>
     </row>
     <row r="6" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="55"/>
@@ -5643,58 +5632,58 @@
       <c r="E23" s="220"/>
     </row>
     <row r="24" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="216" t="s">
+      <c r="A24" s="218" t="s">
         <v>201</v>
       </c>
-      <c r="B24" s="216"/>
-      <c r="C24" s="216"/>
-      <c r="D24" s="216"/>
-      <c r="E24" s="216"/>
+      <c r="B24" s="218"/>
+      <c r="C24" s="218"/>
+      <c r="D24" s="218"/>
+      <c r="E24" s="218"/>
     </row>
     <row r="25" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="215" t="s">
+      <c r="A25" s="217" t="s">
         <v>117</v>
       </c>
-      <c r="B25" s="215"/>
-      <c r="C25" s="215"/>
-      <c r="D25" s="215"/>
-      <c r="E25" s="215"/>
+      <c r="B25" s="217"/>
+      <c r="C25" s="217"/>
+      <c r="D25" s="217"/>
+      <c r="E25" s="217"/>
     </row>
     <row r="26" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="216" t="s">
+      <c r="A26" s="218" t="s">
         <v>134</v>
       </c>
-      <c r="B26" s="216"/>
-      <c r="C26" s="216"/>
-      <c r="D26" s="216"/>
-      <c r="E26" s="216"/>
+      <c r="B26" s="218"/>
+      <c r="C26" s="218"/>
+      <c r="D26" s="218"/>
+      <c r="E26" s="218"/>
     </row>
     <row r="27" spans="1:5" s="81" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="216" t="s">
+      <c r="A27" s="218" t="s">
         <v>135</v>
       </c>
-      <c r="B27" s="216"/>
-      <c r="C27" s="216"/>
-      <c r="D27" s="216"/>
-      <c r="E27" s="216"/>
+      <c r="B27" s="218"/>
+      <c r="C27" s="218"/>
+      <c r="D27" s="218"/>
+      <c r="E27" s="218"/>
     </row>
     <row r="28" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="215" t="s">
+      <c r="A28" s="217" t="s">
         <v>119</v>
       </c>
-      <c r="B28" s="215"/>
-      <c r="C28" s="215"/>
-      <c r="D28" s="215"/>
-      <c r="E28" s="215"/>
+      <c r="B28" s="217"/>
+      <c r="C28" s="217"/>
+      <c r="D28" s="217"/>
+      <c r="E28" s="217"/>
     </row>
     <row r="29" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="215" t="s">
+      <c r="A29" s="217" t="s">
         <v>120</v>
       </c>
-      <c r="B29" s="215"/>
-      <c r="C29" s="215"/>
-      <c r="D29" s="215"/>
-      <c r="E29" s="215"/>
+      <c r="B29" s="217"/>
+      <c r="C29" s="217"/>
+      <c r="D29" s="217"/>
+      <c r="E29" s="217"/>
     </row>
     <row r="30" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15"/>
@@ -5746,80 +5735,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="218" t="s">
+      <c r="A1" s="215" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="218"/>
-      <c r="C1" s="218"/>
-      <c r="D1" s="218"/>
-      <c r="E1" s="218"/>
-      <c r="F1" s="218"/>
-      <c r="G1" s="218"/>
-      <c r="H1" s="218"/>
-      <c r="I1" s="218"/>
-      <c r="J1" s="218"/>
-      <c r="K1" s="218"/>
-      <c r="L1" s="218"/>
-      <c r="M1" s="218"/>
-      <c r="N1" s="218"/>
-      <c r="O1" s="218"/>
+      <c r="B1" s="215"/>
+      <c r="C1" s="215"/>
+      <c r="D1" s="215"/>
+      <c r="E1" s="215"/>
+      <c r="F1" s="215"/>
+      <c r="G1" s="215"/>
+      <c r="H1" s="215"/>
+      <c r="I1" s="215"/>
+      <c r="J1" s="215"/>
+      <c r="K1" s="215"/>
+      <c r="L1" s="215"/>
+      <c r="M1" s="215"/>
+      <c r="N1" s="215"/>
+      <c r="O1" s="215"/>
     </row>
     <row r="2" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="218" t="s">
+      <c r="A2" s="215" t="s">
         <v>191</v>
       </c>
-      <c r="B2" s="218"/>
-      <c r="C2" s="218"/>
-      <c r="D2" s="218"/>
-      <c r="E2" s="218"/>
-      <c r="F2" s="218"/>
-      <c r="G2" s="218"/>
-      <c r="H2" s="218"/>
-      <c r="I2" s="218"/>
-      <c r="J2" s="218"/>
-      <c r="K2" s="218"/>
-      <c r="L2" s="218"/>
-      <c r="M2" s="218"/>
-      <c r="N2" s="218"/>
-      <c r="O2" s="218"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
+      <c r="M2" s="215"/>
+      <c r="N2" s="215"/>
+      <c r="O2" s="215"/>
     </row>
     <row r="3" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="218"/>
-      <c r="B3" s="218"/>
-      <c r="C3" s="218"/>
-      <c r="D3" s="218"/>
-      <c r="E3" s="218"/>
-      <c r="F3" s="218"/>
-      <c r="G3" s="218"/>
-      <c r="H3" s="218"/>
-      <c r="I3" s="218"/>
-      <c r="J3" s="218"/>
-      <c r="K3" s="218"/>
-      <c r="L3" s="218"/>
-      <c r="M3" s="218"/>
-      <c r="N3" s="218"/>
-      <c r="O3" s="218"/>
+      <c r="A3" s="215"/>
+      <c r="B3" s="215"/>
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="215"/>
+      <c r="G3" s="215"/>
+      <c r="H3" s="215"/>
+      <c r="I3" s="215"/>
+      <c r="J3" s="215"/>
+      <c r="K3" s="215"/>
+      <c r="L3" s="215"/>
+      <c r="M3" s="215"/>
+      <c r="N3" s="215"/>
+      <c r="O3" s="215"/>
     </row>
     <row r="4" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="132"/>
       <c r="B4" s="132"/>
       <c r="C4" s="132"/>
       <c r="D4" s="132"/>
-      <c r="E4" s="224" t="s">
+      <c r="E4" s="221" t="s">
         <v>136</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="224"/>
-      <c r="H4" s="224"/>
-      <c r="I4" s="224"/>
+      <c r="F4" s="221"/>
+      <c r="G4" s="221"/>
+      <c r="H4" s="221"/>
+      <c r="I4" s="221"/>
       <c r="J4" s="133"/>
-      <c r="K4" s="224" t="s">
+      <c r="K4" s="221" t="s">
         <v>152</v>
       </c>
-      <c r="L4" s="224"/>
-      <c r="M4" s="224"/>
-      <c r="N4" s="224"/>
-      <c r="O4" s="224"/>
+      <c r="L4" s="221"/>
+      <c r="M4" s="221"/>
+      <c r="N4" s="221"/>
+      <c r="O4" s="221"/>
     </row>
     <row r="5" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="36"/>
@@ -5904,7 +5893,7 @@
     </row>
     <row r="8" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="184" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B8" s="122"/>
       <c r="C8" s="38" t="s">
@@ -6152,7 +6141,7 @@
     </row>
     <row r="16" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="40" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B16" s="38"/>
       <c r="C16" s="38"/>
@@ -6171,7 +6160,7 @@
     </row>
     <row r="17" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="184" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B17" s="122"/>
       <c r="C17" s="38" t="s">
@@ -6354,211 +6343,211 @@
       </c>
     </row>
     <row r="23" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="221" t="s">
+      <c r="A23" s="222" t="s">
         <v>199</v>
       </c>
-      <c r="B23" s="221"/>
-      <c r="C23" s="221"/>
-      <c r="D23" s="221"/>
-      <c r="E23" s="221"/>
-      <c r="F23" s="221"/>
-      <c r="G23" s="221"/>
-      <c r="H23" s="221"/>
-      <c r="I23" s="221"/>
-      <c r="J23" s="221"/>
-      <c r="K23" s="221"/>
-      <c r="L23" s="221"/>
-      <c r="M23" s="221"/>
-      <c r="N23" s="221"/>
-      <c r="O23" s="221"/>
+      <c r="B23" s="222"/>
+      <c r="C23" s="222"/>
+      <c r="D23" s="222"/>
+      <c r="E23" s="222"/>
+      <c r="F23" s="222"/>
+      <c r="G23" s="222"/>
+      <c r="H23" s="222"/>
+      <c r="I23" s="222"/>
+      <c r="J23" s="222"/>
+      <c r="K23" s="222"/>
+      <c r="L23" s="222"/>
+      <c r="M23" s="222"/>
+      <c r="N23" s="222"/>
+      <c r="O23" s="222"/>
     </row>
     <row r="24" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="215" t="s">
+      <c r="A24" s="217" t="s">
         <v>165</v>
       </c>
-      <c r="B24" s="215"/>
-      <c r="C24" s="215"/>
-      <c r="D24" s="215"/>
-      <c r="E24" s="215"/>
-      <c r="F24" s="215"/>
-      <c r="G24" s="215"/>
-      <c r="H24" s="215"/>
-      <c r="I24" s="215"/>
-      <c r="J24" s="215"/>
-      <c r="K24" s="215"/>
-      <c r="L24" s="215"/>
-      <c r="M24" s="215"/>
-      <c r="N24" s="215"/>
-      <c r="O24" s="215"/>
+      <c r="B24" s="217"/>
+      <c r="C24" s="217"/>
+      <c r="D24" s="217"/>
+      <c r="E24" s="217"/>
+      <c r="F24" s="217"/>
+      <c r="G24" s="217"/>
+      <c r="H24" s="217"/>
+      <c r="I24" s="217"/>
+      <c r="J24" s="217"/>
+      <c r="K24" s="217"/>
+      <c r="L24" s="217"/>
+      <c r="M24" s="217"/>
+      <c r="N24" s="217"/>
+      <c r="O24" s="217"/>
     </row>
     <row r="25" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="215" t="s">
+      <c r="A25" s="217" t="s">
         <v>121</v>
       </c>
-      <c r="B25" s="215"/>
-      <c r="C25" s="215"/>
-      <c r="D25" s="215"/>
-      <c r="E25" s="215"/>
-      <c r="F25" s="215"/>
-      <c r="G25" s="215"/>
-      <c r="H25" s="215"/>
-      <c r="I25" s="215"/>
-      <c r="J25" s="215"/>
-      <c r="K25" s="215"/>
-      <c r="L25" s="215"/>
-      <c r="M25" s="215"/>
-      <c r="N25" s="215"/>
-      <c r="O25" s="215"/>
+      <c r="B25" s="217"/>
+      <c r="C25" s="217"/>
+      <c r="D25" s="217"/>
+      <c r="E25" s="217"/>
+      <c r="F25" s="217"/>
+      <c r="G25" s="217"/>
+      <c r="H25" s="217"/>
+      <c r="I25" s="217"/>
+      <c r="J25" s="217"/>
+      <c r="K25" s="217"/>
+      <c r="L25" s="217"/>
+      <c r="M25" s="217"/>
+      <c r="N25" s="217"/>
+      <c r="O25" s="217"/>
     </row>
     <row r="26" spans="1:15" s="81" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="215" t="s">
+      <c r="A26" s="217" t="s">
         <v>192</v>
       </c>
-      <c r="B26" s="215"/>
-      <c r="C26" s="215"/>
-      <c r="D26" s="215"/>
-      <c r="E26" s="215"/>
-      <c r="F26" s="215"/>
-      <c r="G26" s="215"/>
-      <c r="H26" s="215"/>
-      <c r="I26" s="215"/>
-      <c r="J26" s="215"/>
-      <c r="K26" s="215"/>
-      <c r="L26" s="215"/>
-      <c r="M26" s="215"/>
-      <c r="N26" s="215"/>
-      <c r="O26" s="215"/>
+      <c r="B26" s="217"/>
+      <c r="C26" s="217"/>
+      <c r="D26" s="217"/>
+      <c r="E26" s="217"/>
+      <c r="F26" s="217"/>
+      <c r="G26" s="217"/>
+      <c r="H26" s="217"/>
+      <c r="I26" s="217"/>
+      <c r="J26" s="217"/>
+      <c r="K26" s="217"/>
+      <c r="L26" s="217"/>
+      <c r="M26" s="217"/>
+      <c r="N26" s="217"/>
+      <c r="O26" s="217"/>
     </row>
     <row r="27" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="215" t="s">
+      <c r="A27" s="217" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="215"/>
-      <c r="C27" s="215"/>
-      <c r="D27" s="215"/>
-      <c r="E27" s="215"/>
-      <c r="F27" s="215"/>
-      <c r="G27" s="215"/>
-      <c r="H27" s="215"/>
-      <c r="I27" s="215"/>
-      <c r="J27" s="215"/>
-      <c r="K27" s="215"/>
-      <c r="L27" s="215"/>
-      <c r="M27" s="215"/>
-      <c r="N27" s="215"/>
-      <c r="O27" s="215"/>
+      <c r="B27" s="217"/>
+      <c r="C27" s="217"/>
+      <c r="D27" s="217"/>
+      <c r="E27" s="217"/>
+      <c r="F27" s="217"/>
+      <c r="G27" s="217"/>
+      <c r="H27" s="217"/>
+      <c r="I27" s="217"/>
+      <c r="J27" s="217"/>
+      <c r="K27" s="217"/>
+      <c r="L27" s="217"/>
+      <c r="M27" s="217"/>
+      <c r="N27" s="217"/>
+      <c r="O27" s="217"/>
     </row>
     <row r="28" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="215" t="s">
+      <c r="A28" s="217" t="s">
         <v>197</v>
       </c>
-      <c r="B28" s="215"/>
-      <c r="C28" s="215"/>
-      <c r="D28" s="215"/>
-      <c r="E28" s="215"/>
-      <c r="F28" s="215"/>
-      <c r="G28" s="215"/>
-      <c r="H28" s="215"/>
-      <c r="I28" s="215"/>
-      <c r="J28" s="215"/>
-      <c r="K28" s="215"/>
-      <c r="L28" s="215"/>
-      <c r="M28" s="215"/>
-      <c r="N28" s="215"/>
-      <c r="O28" s="215"/>
+      <c r="B28" s="217"/>
+      <c r="C28" s="217"/>
+      <c r="D28" s="217"/>
+      <c r="E28" s="217"/>
+      <c r="F28" s="217"/>
+      <c r="G28" s="217"/>
+      <c r="H28" s="217"/>
+      <c r="I28" s="217"/>
+      <c r="J28" s="217"/>
+      <c r="K28" s="217"/>
+      <c r="L28" s="217"/>
+      <c r="M28" s="217"/>
+      <c r="N28" s="217"/>
+      <c r="O28" s="217"/>
     </row>
     <row r="29" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="215" t="s">
+      <c r="A29" s="217" t="s">
+        <v>244</v>
+      </c>
+      <c r="B29" s="217"/>
+      <c r="C29" s="217"/>
+      <c r="D29" s="224"/>
+      <c r="E29" s="224"/>
+      <c r="F29" s="224"/>
+      <c r="G29" s="224"/>
+      <c r="H29" s="224"/>
+      <c r="I29" s="224"/>
+      <c r="J29" s="224"/>
+      <c r="K29" s="224"/>
+      <c r="L29" s="224"/>
+      <c r="M29" s="224"/>
+      <c r="N29" s="224"/>
+      <c r="O29" s="224"/>
+    </row>
+    <row r="30" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="217" t="s">
         <v>245</v>
       </c>
-      <c r="B29" s="215"/>
-      <c r="C29" s="215"/>
-      <c r="D29" s="223"/>
-      <c r="E29" s="223"/>
-      <c r="F29" s="223"/>
-      <c r="G29" s="223"/>
-      <c r="H29" s="223"/>
-      <c r="I29" s="223"/>
-      <c r="J29" s="223"/>
-      <c r="K29" s="223"/>
-      <c r="L29" s="223"/>
-      <c r="M29" s="223"/>
-      <c r="N29" s="223"/>
-      <c r="O29" s="223"/>
-    </row>
-    <row r="30" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="215" t="s">
-        <v>246</v>
-      </c>
-      <c r="B30" s="215"/>
-      <c r="C30" s="215"/>
-      <c r="D30" s="215"/>
-      <c r="E30" s="215"/>
-      <c r="F30" s="215"/>
-      <c r="G30" s="215"/>
-      <c r="H30" s="215"/>
-      <c r="I30" s="215"/>
-      <c r="J30" s="215"/>
-      <c r="K30" s="215"/>
-      <c r="L30" s="215"/>
-      <c r="M30" s="215"/>
-      <c r="N30" s="215"/>
-      <c r="O30" s="215"/>
+      <c r="B30" s="217"/>
+      <c r="C30" s="217"/>
+      <c r="D30" s="217"/>
+      <c r="E30" s="217"/>
+      <c r="F30" s="217"/>
+      <c r="G30" s="217"/>
+      <c r="H30" s="217"/>
+      <c r="I30" s="217"/>
+      <c r="J30" s="217"/>
+      <c r="K30" s="217"/>
+      <c r="L30" s="217"/>
+      <c r="M30" s="217"/>
+      <c r="N30" s="217"/>
+      <c r="O30" s="217"/>
     </row>
     <row r="31" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="215" t="s">
+      <c r="A31" s="217" t="s">
         <v>198</v>
       </c>
-      <c r="B31" s="215"/>
-      <c r="C31" s="215"/>
-      <c r="D31" s="215"/>
-      <c r="E31" s="215"/>
-      <c r="F31" s="215"/>
-      <c r="G31" s="215"/>
-      <c r="H31" s="215"/>
-      <c r="I31" s="215"/>
-      <c r="J31" s="215"/>
-      <c r="K31" s="215"/>
-      <c r="L31" s="215"/>
-      <c r="M31" s="215"/>
-      <c r="N31" s="215"/>
-      <c r="O31" s="215"/>
+      <c r="B31" s="217"/>
+      <c r="C31" s="217"/>
+      <c r="D31" s="217"/>
+      <c r="E31" s="217"/>
+      <c r="F31" s="217"/>
+      <c r="G31" s="217"/>
+      <c r="H31" s="217"/>
+      <c r="I31" s="217"/>
+      <c r="J31" s="217"/>
+      <c r="K31" s="217"/>
+      <c r="L31" s="217"/>
+      <c r="M31" s="217"/>
+      <c r="N31" s="217"/>
+      <c r="O31" s="217"/>
     </row>
     <row r="32" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="222"/>
-      <c r="B32" s="222"/>
-      <c r="C32" s="222"/>
-      <c r="D32" s="222"/>
-      <c r="E32" s="222"/>
-      <c r="F32" s="222"/>
-      <c r="G32" s="222"/>
-      <c r="H32" s="222"/>
-      <c r="I32" s="222"/>
-      <c r="J32" s="222"/>
-      <c r="K32" s="222"/>
-      <c r="L32" s="222"/>
-      <c r="M32" s="222"/>
-      <c r="N32" s="222"/>
-      <c r="O32" s="222"/>
+      <c r="A32" s="223"/>
+      <c r="B32" s="223"/>
+      <c r="C32" s="223"/>
+      <c r="D32" s="223"/>
+      <c r="E32" s="223"/>
+      <c r="F32" s="223"/>
+      <c r="G32" s="223"/>
+      <c r="H32" s="223"/>
+      <c r="I32" s="223"/>
+      <c r="J32" s="223"/>
+      <c r="K32" s="223"/>
+      <c r="L32" s="223"/>
+      <c r="M32" s="223"/>
+      <c r="N32" s="223"/>
+      <c r="O32" s="223"/>
     </row>
     <row r="33" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="215" t="s">
+      <c r="A33" s="217" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="215"/>
-      <c r="C33" s="215"/>
-      <c r="D33" s="215"/>
-      <c r="E33" s="215"/>
-      <c r="F33" s="215"/>
-      <c r="G33" s="215"/>
-      <c r="H33" s="215"/>
-      <c r="I33" s="215"/>
-      <c r="J33" s="215"/>
-      <c r="K33" s="215"/>
-      <c r="L33" s="215"/>
-      <c r="M33" s="215"/>
-      <c r="N33" s="215"/>
-      <c r="O33" s="215"/>
+      <c r="B33" s="217"/>
+      <c r="C33" s="217"/>
+      <c r="D33" s="217"/>
+      <c r="E33" s="217"/>
+      <c r="F33" s="217"/>
+      <c r="G33" s="217"/>
+      <c r="H33" s="217"/>
+      <c r="I33" s="217"/>
+      <c r="J33" s="217"/>
+      <c r="K33" s="217"/>
+      <c r="L33" s="217"/>
+      <c r="M33" s="217"/>
+      <c r="N33" s="217"/>
+      <c r="O33" s="217"/>
     </row>
     <row r="34" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E34" s="22"/>
@@ -6574,11 +6563,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="K4:O4"/>
     <mergeCell ref="A23:O23"/>
     <mergeCell ref="A30:O30"/>
     <mergeCell ref="A31:O31"/>
@@ -6590,6 +6574,11 @@
     <mergeCell ref="A27:O27"/>
     <mergeCell ref="A28:O28"/>
     <mergeCell ref="A29:O29"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="K4:O4"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -6632,192 +6621,192 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="218" t="s">
+      <c r="A1" s="215" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="218"/>
-      <c r="C1" s="218"/>
-      <c r="D1" s="218"/>
-      <c r="E1" s="218"/>
-      <c r="F1" s="218"/>
-      <c r="G1" s="218"/>
-      <c r="H1" s="218"/>
-      <c r="I1" s="218"/>
-      <c r="J1" s="218"/>
-      <c r="K1" s="218"/>
-      <c r="L1" s="218"/>
-      <c r="M1" s="218"/>
-      <c r="N1" s="218"/>
-      <c r="O1" s="218"/>
-      <c r="P1" s="218"/>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="218"/>
-      <c r="Y1" s="218"/>
+      <c r="B1" s="215"/>
+      <c r="C1" s="215"/>
+      <c r="D1" s="215"/>
+      <c r="E1" s="215"/>
+      <c r="F1" s="215"/>
+      <c r="G1" s="215"/>
+      <c r="H1" s="215"/>
+      <c r="I1" s="215"/>
+      <c r="J1" s="215"/>
+      <c r="K1" s="215"/>
+      <c r="L1" s="215"/>
+      <c r="M1" s="215"/>
+      <c r="N1" s="215"/>
+      <c r="O1" s="215"/>
+      <c r="P1" s="215"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="215"/>
+      <c r="Y1" s="215"/>
     </row>
     <row r="2" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="218" t="s">
+      <c r="A2" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="218"/>
-      <c r="C2" s="218"/>
-      <c r="D2" s="218"/>
-      <c r="E2" s="218"/>
-      <c r="F2" s="218"/>
-      <c r="G2" s="218"/>
-      <c r="H2" s="218"/>
-      <c r="I2" s="218"/>
-      <c r="J2" s="218"/>
-      <c r="K2" s="218"/>
-      <c r="L2" s="218"/>
-      <c r="M2" s="218"/>
-      <c r="N2" s="218"/>
-      <c r="O2" s="218"/>
-      <c r="P2" s="218"/>
-      <c r="Q2" s="218"/>
-      <c r="R2" s="218"/>
-      <c r="S2" s="218"/>
-      <c r="T2" s="218"/>
-      <c r="U2" s="218"/>
-      <c r="V2" s="218"/>
-      <c r="W2" s="218"/>
-      <c r="X2" s="218"/>
-      <c r="Y2" s="218"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
+      <c r="M2" s="215"/>
+      <c r="N2" s="215"/>
+      <c r="O2" s="215"/>
+      <c r="P2" s="215"/>
+      <c r="Q2" s="215"/>
+      <c r="R2" s="215"/>
+      <c r="S2" s="215"/>
+      <c r="T2" s="215"/>
+      <c r="U2" s="215"/>
+      <c r="V2" s="215"/>
+      <c r="W2" s="215"/>
+      <c r="X2" s="215"/>
+      <c r="Y2" s="215"/>
     </row>
     <row r="3" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="225"/>
-      <c r="B3" s="225"/>
-      <c r="C3" s="225"/>
-      <c r="D3" s="225"/>
-      <c r="E3" s="225"/>
-      <c r="F3" s="225"/>
-      <c r="G3" s="225"/>
-      <c r="H3" s="225"/>
-      <c r="I3" s="225"/>
-      <c r="J3" s="225"/>
-      <c r="K3" s="225"/>
-      <c r="L3" s="225"/>
-      <c r="M3" s="225"/>
-      <c r="N3" s="225"/>
-      <c r="O3" s="225"/>
-      <c r="P3" s="225"/>
-      <c r="Q3" s="225"/>
-      <c r="R3" s="225"/>
-      <c r="S3" s="225"/>
-      <c r="T3" s="225"/>
-      <c r="U3" s="225"/>
-      <c r="V3" s="225"/>
-      <c r="W3" s="225"/>
-      <c r="X3" s="225"/>
-      <c r="Y3" s="225"/>
+      <c r="A3" s="228"/>
+      <c r="B3" s="228"/>
+      <c r="C3" s="228"/>
+      <c r="D3" s="228"/>
+      <c r="E3" s="228"/>
+      <c r="F3" s="228"/>
+      <c r="G3" s="228"/>
+      <c r="H3" s="228"/>
+      <c r="I3" s="228"/>
+      <c r="J3" s="228"/>
+      <c r="K3" s="228"/>
+      <c r="L3" s="228"/>
+      <c r="M3" s="228"/>
+      <c r="N3" s="228"/>
+      <c r="O3" s="228"/>
+      <c r="P3" s="228"/>
+      <c r="Q3" s="228"/>
+      <c r="R3" s="228"/>
+      <c r="S3" s="228"/>
+      <c r="T3" s="228"/>
+      <c r="U3" s="228"/>
+      <c r="V3" s="228"/>
+      <c r="W3" s="228"/>
+      <c r="X3" s="228"/>
+      <c r="Y3" s="228"/>
     </row>
     <row r="4" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="94"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="229" t="s">
+      <c r="C4" s="226" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="229"/>
-      <c r="E4" s="229"/>
-      <c r="F4" s="229"/>
-      <c r="G4" s="229"/>
+      <c r="D4" s="226"/>
+      <c r="E4" s="226"/>
+      <c r="F4" s="226"/>
+      <c r="G4" s="226"/>
       <c r="H4" s="95"/>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="226" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="229"/>
-      <c r="K4" s="229"/>
-      <c r="L4" s="229"/>
-      <c r="M4" s="229"/>
+      <c r="J4" s="226"/>
+      <c r="K4" s="226"/>
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
       <c r="N4" s="95"/>
-      <c r="O4" s="230" t="s">
+      <c r="O4" s="227" t="s">
         <v>92</v>
       </c>
-      <c r="P4" s="230"/>
-      <c r="Q4" s="230"/>
-      <c r="R4" s="230"/>
-      <c r="S4" s="230"/>
+      <c r="P4" s="227"/>
+      <c r="Q4" s="227"/>
+      <c r="R4" s="227"/>
+      <c r="S4" s="227"/>
       <c r="T4" s="95"/>
-      <c r="U4" s="229" t="s">
+      <c r="U4" s="226" t="s">
         <v>19</v>
       </c>
-      <c r="V4" s="229"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="229"/>
-      <c r="Y4" s="229"/>
+      <c r="V4" s="226"/>
+      <c r="W4" s="226"/>
+      <c r="X4" s="226"/>
+      <c r="Y4" s="226"/>
     </row>
     <row r="5" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="64"/>
       <c r="B5" s="64"/>
-      <c r="C5" s="228" t="s">
+      <c r="C5" s="225" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="228"/>
-      <c r="E5" s="228"/>
+      <c r="D5" s="225"/>
+      <c r="E5" s="225"/>
       <c r="F5" s="95"/>
       <c r="G5" s="95"/>
       <c r="H5" s="36"/>
-      <c r="I5" s="228" t="s">
+      <c r="I5" s="225" t="s">
         <v>93</v>
       </c>
-      <c r="J5" s="228"/>
-      <c r="K5" s="228"/>
+      <c r="J5" s="225"/>
+      <c r="K5" s="225"/>
       <c r="L5" s="95"/>
       <c r="M5" s="95"/>
       <c r="N5" s="36"/>
-      <c r="O5" s="228" t="s">
+      <c r="O5" s="225" t="s">
         <v>93</v>
       </c>
-      <c r="P5" s="228"/>
-      <c r="Q5" s="228"/>
+      <c r="P5" s="225"/>
+      <c r="Q5" s="225"/>
       <c r="R5" s="95"/>
       <c r="S5" s="95"/>
       <c r="T5" s="36"/>
-      <c r="U5" s="228" t="s">
+      <c r="U5" s="225" t="s">
         <v>93</v>
       </c>
-      <c r="V5" s="228"/>
-      <c r="W5" s="228"/>
+      <c r="V5" s="225"/>
+      <c r="W5" s="225"/>
       <c r="X5" s="95"/>
       <c r="Y5" s="95"/>
     </row>
     <row r="6" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="64"/>
       <c r="B6" s="64"/>
-      <c r="C6" s="227" t="s">
+      <c r="C6" s="230" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="227"/>
-      <c r="E6" s="227"/>
+      <c r="D6" s="230"/>
+      <c r="E6" s="230"/>
       <c r="F6" s="36"/>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
-      <c r="I6" s="227" t="s">
+      <c r="I6" s="230" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="227"/>
-      <c r="K6" s="227"/>
+      <c r="J6" s="230"/>
+      <c r="K6" s="230"/>
       <c r="L6" s="36"/>
       <c r="M6" s="36"/>
       <c r="N6" s="36"/>
-      <c r="O6" s="227" t="s">
+      <c r="O6" s="230" t="s">
         <v>28</v>
       </c>
-      <c r="P6" s="227"/>
-      <c r="Q6" s="227"/>
+      <c r="P6" s="230"/>
+      <c r="Q6" s="230"/>
       <c r="R6" s="36"/>
       <c r="S6" s="36"/>
       <c r="T6" s="36"/>
-      <c r="U6" s="227" t="s">
+      <c r="U6" s="230" t="s">
         <v>28</v>
       </c>
-      <c r="V6" s="227"/>
-      <c r="W6" s="227"/>
+      <c r="V6" s="230"/>
+      <c r="W6" s="230"/>
       <c r="X6" s="36"/>
       <c r="Y6" s="36"/>
     </row>
@@ -8227,292 +8216,292 @@
       </c>
     </row>
     <row r="34" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="226" t="s">
+      <c r="A34" s="229" t="s">
         <v>138</v>
       </c>
-      <c r="B34" s="226"/>
-      <c r="C34" s="226"/>
-      <c r="D34" s="226"/>
-      <c r="E34" s="226"/>
-      <c r="F34" s="226"/>
-      <c r="G34" s="226"/>
-      <c r="H34" s="226"/>
-      <c r="I34" s="226"/>
-      <c r="J34" s="226"/>
-      <c r="K34" s="226"/>
-      <c r="L34" s="226"/>
-      <c r="M34" s="226"/>
-      <c r="N34" s="226"/>
-      <c r="O34" s="226"/>
-      <c r="P34" s="226"/>
-      <c r="Q34" s="226"/>
-      <c r="R34" s="226"/>
-      <c r="S34" s="226"/>
-      <c r="T34" s="226"/>
-      <c r="U34" s="226"/>
-      <c r="V34" s="226"/>
-      <c r="W34" s="226"/>
-      <c r="X34" s="226"/>
-      <c r="Y34" s="226"/>
+      <c r="B34" s="229"/>
+      <c r="C34" s="229"/>
+      <c r="D34" s="229"/>
+      <c r="E34" s="229"/>
+      <c r="F34" s="229"/>
+      <c r="G34" s="229"/>
+      <c r="H34" s="229"/>
+      <c r="I34" s="229"/>
+      <c r="J34" s="229"/>
+      <c r="K34" s="229"/>
+      <c r="L34" s="229"/>
+      <c r="M34" s="229"/>
+      <c r="N34" s="229"/>
+      <c r="O34" s="229"/>
+      <c r="P34" s="229"/>
+      <c r="Q34" s="229"/>
+      <c r="R34" s="229"/>
+      <c r="S34" s="229"/>
+      <c r="T34" s="229"/>
+      <c r="U34" s="229"/>
+      <c r="V34" s="229"/>
+      <c r="W34" s="229"/>
+      <c r="X34" s="229"/>
+      <c r="Y34" s="229"/>
     </row>
     <row r="35" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="215" t="s">
+      <c r="A35" s="217" t="s">
         <v>165</v>
       </c>
-      <c r="B35" s="215"/>
-      <c r="C35" s="215"/>
-      <c r="D35" s="215"/>
-      <c r="E35" s="215"/>
-      <c r="F35" s="215"/>
-      <c r="G35" s="215"/>
-      <c r="H35" s="215"/>
-      <c r="I35" s="215"/>
-      <c r="J35" s="215"/>
-      <c r="K35" s="215"/>
-      <c r="L35" s="215"/>
-      <c r="M35" s="215"/>
-      <c r="N35" s="215"/>
-      <c r="O35" s="215"/>
-      <c r="P35" s="215"/>
-      <c r="Q35" s="215"/>
-      <c r="R35" s="215"/>
-      <c r="S35" s="215"/>
-      <c r="T35" s="215"/>
-      <c r="U35" s="215"/>
-      <c r="V35" s="215"/>
-      <c r="W35" s="215"/>
-      <c r="X35" s="215"/>
-      <c r="Y35" s="215"/>
+      <c r="B35" s="217"/>
+      <c r="C35" s="217"/>
+      <c r="D35" s="217"/>
+      <c r="E35" s="217"/>
+      <c r="F35" s="217"/>
+      <c r="G35" s="217"/>
+      <c r="H35" s="217"/>
+      <c r="I35" s="217"/>
+      <c r="J35" s="217"/>
+      <c r="K35" s="217"/>
+      <c r="L35" s="217"/>
+      <c r="M35" s="217"/>
+      <c r="N35" s="217"/>
+      <c r="O35" s="217"/>
+      <c r="P35" s="217"/>
+      <c r="Q35" s="217"/>
+      <c r="R35" s="217"/>
+      <c r="S35" s="217"/>
+      <c r="T35" s="217"/>
+      <c r="U35" s="217"/>
+      <c r="V35" s="217"/>
+      <c r="W35" s="217"/>
+      <c r="X35" s="217"/>
+      <c r="Y35" s="217"/>
     </row>
     <row r="36" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="216" t="s">
+      <c r="A36" s="218" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="216"/>
-      <c r="C36" s="216"/>
-      <c r="D36" s="216"/>
-      <c r="E36" s="216"/>
-      <c r="F36" s="216"/>
-      <c r="G36" s="216"/>
-      <c r="H36" s="216"/>
-      <c r="I36" s="216"/>
-      <c r="J36" s="216"/>
-      <c r="K36" s="216"/>
-      <c r="L36" s="216"/>
-      <c r="M36" s="216"/>
-      <c r="N36" s="216"/>
-      <c r="O36" s="216"/>
-      <c r="P36" s="216"/>
-      <c r="Q36" s="216"/>
-      <c r="R36" s="216"/>
-      <c r="S36" s="216"/>
-      <c r="T36" s="216"/>
-      <c r="U36" s="216"/>
-      <c r="V36" s="216"/>
-      <c r="W36" s="216"/>
-      <c r="X36" s="216"/>
-      <c r="Y36" s="216"/>
+      <c r="B36" s="218"/>
+      <c r="C36" s="218"/>
+      <c r="D36" s="218"/>
+      <c r="E36" s="218"/>
+      <c r="F36" s="218"/>
+      <c r="G36" s="218"/>
+      <c r="H36" s="218"/>
+      <c r="I36" s="218"/>
+      <c r="J36" s="218"/>
+      <c r="K36" s="218"/>
+      <c r="L36" s="218"/>
+      <c r="M36" s="218"/>
+      <c r="N36" s="218"/>
+      <c r="O36" s="218"/>
+      <c r="P36" s="218"/>
+      <c r="Q36" s="218"/>
+      <c r="R36" s="218"/>
+      <c r="S36" s="218"/>
+      <c r="T36" s="218"/>
+      <c r="U36" s="218"/>
+      <c r="V36" s="218"/>
+      <c r="W36" s="218"/>
+      <c r="X36" s="218"/>
+      <c r="Y36" s="218"/>
     </row>
     <row r="37" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="215" t="s">
+      <c r="A37" s="217" t="s">
         <v>124</v>
       </c>
-      <c r="B37" s="215"/>
-      <c r="C37" s="215"/>
-      <c r="D37" s="215"/>
-      <c r="E37" s="215"/>
-      <c r="F37" s="215"/>
-      <c r="G37" s="215"/>
-      <c r="H37" s="215"/>
-      <c r="I37" s="215"/>
-      <c r="J37" s="215"/>
-      <c r="K37" s="215"/>
-      <c r="L37" s="215"/>
-      <c r="M37" s="215"/>
-      <c r="N37" s="215"/>
-      <c r="O37" s="215"/>
-      <c r="P37" s="215"/>
-      <c r="Q37" s="215"/>
-      <c r="R37" s="215"/>
-      <c r="S37" s="215"/>
-      <c r="T37" s="215"/>
-      <c r="U37" s="215"/>
-      <c r="V37" s="215"/>
-      <c r="W37" s="215"/>
-      <c r="X37" s="215"/>
-      <c r="Y37" s="215"/>
+      <c r="B37" s="217"/>
+      <c r="C37" s="217"/>
+      <c r="D37" s="217"/>
+      <c r="E37" s="217"/>
+      <c r="F37" s="217"/>
+      <c r="G37" s="217"/>
+      <c r="H37" s="217"/>
+      <c r="I37" s="217"/>
+      <c r="J37" s="217"/>
+      <c r="K37" s="217"/>
+      <c r="L37" s="217"/>
+      <c r="M37" s="217"/>
+      <c r="N37" s="217"/>
+      <c r="O37" s="217"/>
+      <c r="P37" s="217"/>
+      <c r="Q37" s="217"/>
+      <c r="R37" s="217"/>
+      <c r="S37" s="217"/>
+      <c r="T37" s="217"/>
+      <c r="U37" s="217"/>
+      <c r="V37" s="217"/>
+      <c r="W37" s="217"/>
+      <c r="X37" s="217"/>
+      <c r="Y37" s="217"/>
     </row>
     <row r="38" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="215" t="s">
+      <c r="A38" s="217" t="s">
         <v>125</v>
       </c>
-      <c r="B38" s="215"/>
-      <c r="C38" s="215"/>
-      <c r="D38" s="215"/>
-      <c r="E38" s="215"/>
-      <c r="F38" s="215"/>
-      <c r="G38" s="215"/>
-      <c r="H38" s="215"/>
-      <c r="I38" s="215"/>
-      <c r="J38" s="215"/>
-      <c r="K38" s="215"/>
-      <c r="L38" s="215"/>
-      <c r="M38" s="215"/>
-      <c r="N38" s="215"/>
-      <c r="O38" s="215"/>
-      <c r="P38" s="215"/>
-      <c r="Q38" s="215"/>
-      <c r="R38" s="215"/>
-      <c r="S38" s="215"/>
-      <c r="T38" s="215"/>
-      <c r="U38" s="215"/>
-      <c r="V38" s="215"/>
-      <c r="W38" s="215"/>
-      <c r="X38" s="215"/>
-      <c r="Y38" s="215"/>
+      <c r="B38" s="217"/>
+      <c r="C38" s="217"/>
+      <c r="D38" s="217"/>
+      <c r="E38" s="217"/>
+      <c r="F38" s="217"/>
+      <c r="G38" s="217"/>
+      <c r="H38" s="217"/>
+      <c r="I38" s="217"/>
+      <c r="J38" s="217"/>
+      <c r="K38" s="217"/>
+      <c r="L38" s="217"/>
+      <c r="M38" s="217"/>
+      <c r="N38" s="217"/>
+      <c r="O38" s="217"/>
+      <c r="P38" s="217"/>
+      <c r="Q38" s="217"/>
+      <c r="R38" s="217"/>
+      <c r="S38" s="217"/>
+      <c r="T38" s="217"/>
+      <c r="U38" s="217"/>
+      <c r="V38" s="217"/>
+      <c r="W38" s="217"/>
+      <c r="X38" s="217"/>
+      <c r="Y38" s="217"/>
     </row>
     <row r="39" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="215" t="s">
+      <c r="A39" s="217" t="s">
         <v>146</v>
       </c>
-      <c r="B39" s="215"/>
-      <c r="C39" s="215"/>
-      <c r="D39" s="215"/>
-      <c r="E39" s="215"/>
-      <c r="F39" s="215"/>
-      <c r="G39" s="215"/>
-      <c r="H39" s="215"/>
-      <c r="I39" s="215"/>
-      <c r="J39" s="215"/>
-      <c r="K39" s="215"/>
-      <c r="L39" s="215"/>
-      <c r="M39" s="215"/>
-      <c r="N39" s="215"/>
-      <c r="O39" s="215"/>
-      <c r="P39" s="215"/>
-      <c r="Q39" s="215"/>
-      <c r="R39" s="215"/>
-      <c r="S39" s="215"/>
-      <c r="T39" s="215"/>
-      <c r="U39" s="215"/>
-      <c r="V39" s="215"/>
-      <c r="W39" s="215"/>
-      <c r="X39" s="215"/>
-      <c r="Y39" s="215"/>
+      <c r="B39" s="217"/>
+      <c r="C39" s="217"/>
+      <c r="D39" s="217"/>
+      <c r="E39" s="217"/>
+      <c r="F39" s="217"/>
+      <c r="G39" s="217"/>
+      <c r="H39" s="217"/>
+      <c r="I39" s="217"/>
+      <c r="J39" s="217"/>
+      <c r="K39" s="217"/>
+      <c r="L39" s="217"/>
+      <c r="M39" s="217"/>
+      <c r="N39" s="217"/>
+      <c r="O39" s="217"/>
+      <c r="P39" s="217"/>
+      <c r="Q39" s="217"/>
+      <c r="R39" s="217"/>
+      <c r="S39" s="217"/>
+      <c r="T39" s="217"/>
+      <c r="U39" s="217"/>
+      <c r="V39" s="217"/>
+      <c r="W39" s="217"/>
+      <c r="X39" s="217"/>
+      <c r="Y39" s="217"/>
     </row>
     <row r="40" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="215" t="s">
+      <c r="A40" s="217" t="s">
         <v>126</v>
       </c>
-      <c r="B40" s="215"/>
-      <c r="C40" s="215"/>
-      <c r="D40" s="215"/>
-      <c r="E40" s="215"/>
-      <c r="F40" s="215"/>
-      <c r="G40" s="215"/>
-      <c r="H40" s="215"/>
-      <c r="I40" s="215"/>
-      <c r="J40" s="215"/>
-      <c r="K40" s="215"/>
-      <c r="L40" s="215"/>
-      <c r="M40" s="215"/>
-      <c r="N40" s="215"/>
-      <c r="O40" s="215"/>
-      <c r="P40" s="215"/>
-      <c r="Q40" s="215"/>
-      <c r="R40" s="215"/>
-      <c r="S40" s="215"/>
-      <c r="T40" s="215"/>
-      <c r="U40" s="215"/>
-      <c r="V40" s="215"/>
-      <c r="W40" s="215"/>
-      <c r="X40" s="215"/>
-      <c r="Y40" s="215"/>
+      <c r="B40" s="217"/>
+      <c r="C40" s="217"/>
+      <c r="D40" s="217"/>
+      <c r="E40" s="217"/>
+      <c r="F40" s="217"/>
+      <c r="G40" s="217"/>
+      <c r="H40" s="217"/>
+      <c r="I40" s="217"/>
+      <c r="J40" s="217"/>
+      <c r="K40" s="217"/>
+      <c r="L40" s="217"/>
+      <c r="M40" s="217"/>
+      <c r="N40" s="217"/>
+      <c r="O40" s="217"/>
+      <c r="P40" s="217"/>
+      <c r="Q40" s="217"/>
+      <c r="R40" s="217"/>
+      <c r="S40" s="217"/>
+      <c r="T40" s="217"/>
+      <c r="U40" s="217"/>
+      <c r="V40" s="217"/>
+      <c r="W40" s="217"/>
+      <c r="X40" s="217"/>
+      <c r="Y40" s="217"/>
     </row>
     <row r="41" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="215" t="s">
+      <c r="A41" s="217" t="s">
         <v>127</v>
       </c>
-      <c r="B41" s="215"/>
-      <c r="C41" s="215"/>
-      <c r="D41" s="215"/>
-      <c r="E41" s="215"/>
-      <c r="F41" s="215"/>
-      <c r="G41" s="215"/>
-      <c r="H41" s="215"/>
-      <c r="I41" s="215"/>
-      <c r="J41" s="215"/>
-      <c r="K41" s="215"/>
-      <c r="L41" s="215"/>
-      <c r="M41" s="215"/>
-      <c r="N41" s="215"/>
-      <c r="O41" s="215"/>
-      <c r="P41" s="215"/>
-      <c r="Q41" s="215"/>
-      <c r="R41" s="215"/>
-      <c r="S41" s="215"/>
-      <c r="T41" s="215"/>
-      <c r="U41" s="215"/>
-      <c r="V41" s="215"/>
-      <c r="W41" s="215"/>
-      <c r="X41" s="215"/>
-      <c r="Y41" s="215"/>
+      <c r="B41" s="217"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="217"/>
+      <c r="E41" s="217"/>
+      <c r="F41" s="217"/>
+      <c r="G41" s="217"/>
+      <c r="H41" s="217"/>
+      <c r="I41" s="217"/>
+      <c r="J41" s="217"/>
+      <c r="K41" s="217"/>
+      <c r="L41" s="217"/>
+      <c r="M41" s="217"/>
+      <c r="N41" s="217"/>
+      <c r="O41" s="217"/>
+      <c r="P41" s="217"/>
+      <c r="Q41" s="217"/>
+      <c r="R41" s="217"/>
+      <c r="S41" s="217"/>
+      <c r="T41" s="217"/>
+      <c r="U41" s="217"/>
+      <c r="V41" s="217"/>
+      <c r="W41" s="217"/>
+      <c r="X41" s="217"/>
+      <c r="Y41" s="217"/>
     </row>
     <row r="42" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="215"/>
-      <c r="B42" s="215"/>
-      <c r="C42" s="215"/>
-      <c r="D42" s="215"/>
-      <c r="E42" s="215"/>
-      <c r="F42" s="215"/>
-      <c r="G42" s="215"/>
-      <c r="H42" s="215"/>
-      <c r="I42" s="215"/>
-      <c r="J42" s="215"/>
-      <c r="K42" s="215"/>
-      <c r="L42" s="215"/>
-      <c r="M42" s="215"/>
-      <c r="N42" s="215"/>
-      <c r="O42" s="215"/>
-      <c r="P42" s="215"/>
-      <c r="Q42" s="215"/>
-      <c r="R42" s="215"/>
-      <c r="S42" s="215"/>
-      <c r="T42" s="215"/>
-      <c r="U42" s="215"/>
-      <c r="V42" s="215"/>
-      <c r="W42" s="215"/>
-      <c r="X42" s="215"/>
-      <c r="Y42" s="215"/>
+      <c r="A42" s="217"/>
+      <c r="B42" s="217"/>
+      <c r="C42" s="217"/>
+      <c r="D42" s="217"/>
+      <c r="E42" s="217"/>
+      <c r="F42" s="217"/>
+      <c r="G42" s="217"/>
+      <c r="H42" s="217"/>
+      <c r="I42" s="217"/>
+      <c r="J42" s="217"/>
+      <c r="K42" s="217"/>
+      <c r="L42" s="217"/>
+      <c r="M42" s="217"/>
+      <c r="N42" s="217"/>
+      <c r="O42" s="217"/>
+      <c r="P42" s="217"/>
+      <c r="Q42" s="217"/>
+      <c r="R42" s="217"/>
+      <c r="S42" s="217"/>
+      <c r="T42" s="217"/>
+      <c r="U42" s="217"/>
+      <c r="V42" s="217"/>
+      <c r="W42" s="217"/>
+      <c r="X42" s="217"/>
+      <c r="Y42" s="217"/>
     </row>
     <row r="43" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="215" t="s">
+      <c r="A43" s="217" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="215"/>
-      <c r="C43" s="215"/>
-      <c r="D43" s="215"/>
-      <c r="E43" s="215"/>
-      <c r="F43" s="215"/>
-      <c r="G43" s="215"/>
-      <c r="H43" s="215"/>
-      <c r="I43" s="215"/>
-      <c r="J43" s="215"/>
-      <c r="K43" s="215"/>
-      <c r="L43" s="215"/>
-      <c r="M43" s="215"/>
-      <c r="N43" s="215"/>
-      <c r="O43" s="215"/>
-      <c r="P43" s="215"/>
-      <c r="Q43" s="215"/>
-      <c r="R43" s="215"/>
-      <c r="S43" s="215"/>
-      <c r="T43" s="215"/>
-      <c r="U43" s="215"/>
-      <c r="V43" s="215"/>
-      <c r="W43" s="215"/>
-      <c r="X43" s="215"/>
-      <c r="Y43" s="215"/>
+      <c r="B43" s="217"/>
+      <c r="C43" s="217"/>
+      <c r="D43" s="217"/>
+      <c r="E43" s="217"/>
+      <c r="F43" s="217"/>
+      <c r="G43" s="217"/>
+      <c r="H43" s="217"/>
+      <c r="I43" s="217"/>
+      <c r="J43" s="217"/>
+      <c r="K43" s="217"/>
+      <c r="L43" s="217"/>
+      <c r="M43" s="217"/>
+      <c r="N43" s="217"/>
+      <c r="O43" s="217"/>
+      <c r="P43" s="217"/>
+      <c r="Q43" s="217"/>
+      <c r="R43" s="217"/>
+      <c r="S43" s="217"/>
+      <c r="T43" s="217"/>
+      <c r="U43" s="217"/>
+      <c r="V43" s="217"/>
+      <c r="W43" s="217"/>
+      <c r="X43" s="217"/>
+      <c r="Y43" s="217"/>
     </row>
     <row r="44" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="26"/>
@@ -8627,15 +8616,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="U5:W5"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="U4:Y4"/>
     <mergeCell ref="A43:Y43"/>
     <mergeCell ref="A2:Y2"/>
     <mergeCell ref="A3:Y3"/>
@@ -8652,6 +8632,15 @@
     <mergeCell ref="A40:Y40"/>
     <mergeCell ref="A41:Y41"/>
     <mergeCell ref="A42:Y42"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="U5:W5"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="U4:Y4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>
@@ -8697,234 +8686,234 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="218" t="s">
+      <c r="A1" s="215" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="218"/>
-      <c r="C1" s="218"/>
-      <c r="D1" s="218"/>
-      <c r="E1" s="218"/>
-      <c r="F1" s="218"/>
-      <c r="G1" s="218"/>
-      <c r="H1" s="218"/>
-      <c r="I1" s="218"/>
-      <c r="J1" s="218"/>
-      <c r="K1" s="218"/>
-      <c r="L1" s="218"/>
-      <c r="M1" s="218"/>
-      <c r="N1" s="218"/>
-      <c r="O1" s="218"/>
-      <c r="P1" s="218"/>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="218"/>
-      <c r="Y1" s="218"/>
-      <c r="Z1" s="218"/>
-      <c r="AA1" s="218"/>
-      <c r="AB1" s="218"/>
-      <c r="AC1" s="218"/>
-      <c r="AD1" s="218"/>
-      <c r="AE1" s="218"/>
+      <c r="B1" s="215"/>
+      <c r="C1" s="215"/>
+      <c r="D1" s="215"/>
+      <c r="E1" s="215"/>
+      <c r="F1" s="215"/>
+      <c r="G1" s="215"/>
+      <c r="H1" s="215"/>
+      <c r="I1" s="215"/>
+      <c r="J1" s="215"/>
+      <c r="K1" s="215"/>
+      <c r="L1" s="215"/>
+      <c r="M1" s="215"/>
+      <c r="N1" s="215"/>
+      <c r="O1" s="215"/>
+      <c r="P1" s="215"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="215"/>
+      <c r="Y1" s="215"/>
+      <c r="Z1" s="215"/>
+      <c r="AA1" s="215"/>
+      <c r="AB1" s="215"/>
+      <c r="AC1" s="215"/>
+      <c r="AD1" s="215"/>
+      <c r="AE1" s="215"/>
     </row>
     <row r="2" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="218" t="s">
+      <c r="A2" s="215" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="218"/>
-      <c r="C2" s="218"/>
-      <c r="D2" s="218"/>
-      <c r="E2" s="218"/>
-      <c r="F2" s="218"/>
-      <c r="G2" s="218"/>
-      <c r="H2" s="218"/>
-      <c r="I2" s="218"/>
-      <c r="J2" s="218"/>
-      <c r="K2" s="218"/>
-      <c r="L2" s="218"/>
-      <c r="M2" s="218"/>
-      <c r="N2" s="218"/>
-      <c r="O2" s="218"/>
-      <c r="P2" s="218"/>
-      <c r="Q2" s="218"/>
-      <c r="R2" s="218"/>
-      <c r="S2" s="218"/>
-      <c r="T2" s="218"/>
-      <c r="U2" s="218"/>
-      <c r="V2" s="218"/>
-      <c r="W2" s="218"/>
-      <c r="X2" s="218"/>
-      <c r="Y2" s="218"/>
-      <c r="Z2" s="218"/>
-      <c r="AA2" s="218"/>
-      <c r="AB2" s="218"/>
-      <c r="AC2" s="218"/>
-      <c r="AD2" s="218"/>
-      <c r="AE2" s="218"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
+      <c r="M2" s="215"/>
+      <c r="N2" s="215"/>
+      <c r="O2" s="215"/>
+      <c r="P2" s="215"/>
+      <c r="Q2" s="215"/>
+      <c r="R2" s="215"/>
+      <c r="S2" s="215"/>
+      <c r="T2" s="215"/>
+      <c r="U2" s="215"/>
+      <c r="V2" s="215"/>
+      <c r="W2" s="215"/>
+      <c r="X2" s="215"/>
+      <c r="Y2" s="215"/>
+      <c r="Z2" s="215"/>
+      <c r="AA2" s="215"/>
+      <c r="AB2" s="215"/>
+      <c r="AC2" s="215"/>
+      <c r="AD2" s="215"/>
+      <c r="AE2" s="215"/>
     </row>
     <row r="3" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="231"/>
-      <c r="B3" s="231"/>
-      <c r="C3" s="231"/>
-      <c r="D3" s="231"/>
-      <c r="E3" s="231"/>
-      <c r="F3" s="231"/>
-      <c r="G3" s="231"/>
-      <c r="H3" s="231"/>
-      <c r="I3" s="231"/>
-      <c r="J3" s="231"/>
-      <c r="K3" s="231"/>
-      <c r="L3" s="231"/>
-      <c r="M3" s="231"/>
-      <c r="N3" s="231"/>
-      <c r="O3" s="231"/>
-      <c r="P3" s="231"/>
-      <c r="Q3" s="231"/>
-      <c r="R3" s="231"/>
-      <c r="S3" s="231"/>
-      <c r="T3" s="231"/>
-      <c r="U3" s="231"/>
-      <c r="V3" s="231"/>
-      <c r="W3" s="231"/>
-      <c r="X3" s="231"/>
-      <c r="Y3" s="231"/>
-      <c r="Z3" s="231"/>
-      <c r="AA3" s="231"/>
-      <c r="AB3" s="231"/>
-      <c r="AC3" s="231"/>
-      <c r="AD3" s="231"/>
-      <c r="AE3" s="231"/>
+      <c r="A3" s="232"/>
+      <c r="B3" s="232"/>
+      <c r="C3" s="232"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="232"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
+      <c r="M3" s="232"/>
+      <c r="N3" s="232"/>
+      <c r="O3" s="232"/>
+      <c r="P3" s="232"/>
+      <c r="Q3" s="232"/>
+      <c r="R3" s="232"/>
+      <c r="S3" s="232"/>
+      <c r="T3" s="232"/>
+      <c r="U3" s="232"/>
+      <c r="V3" s="232"/>
+      <c r="W3" s="232"/>
+      <c r="X3" s="232"/>
+      <c r="Y3" s="232"/>
+      <c r="Z3" s="232"/>
+      <c r="AA3" s="232"/>
+      <c r="AB3" s="232"/>
+      <c r="AC3" s="232"/>
+      <c r="AD3" s="232"/>
+      <c r="AE3" s="232"/>
     </row>
     <row r="4" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="64"/>
       <c r="B4" s="36"/>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="233" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="232"/>
-      <c r="E4" s="232"/>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
+      <c r="D4" s="233"/>
+      <c r="E4" s="233"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
       <c r="H4" s="36"/>
-      <c r="I4" s="232" t="s">
+      <c r="I4" s="233" t="s">
         <v>94</v>
       </c>
-      <c r="J4" s="232"/>
-      <c r="K4" s="232"/>
-      <c r="L4" s="232"/>
-      <c r="M4" s="232"/>
+      <c r="J4" s="233"/>
+      <c r="K4" s="233"/>
+      <c r="L4" s="233"/>
+      <c r="M4" s="233"/>
       <c r="N4" s="36"/>
-      <c r="O4" s="227" t="s">
+      <c r="O4" s="230" t="s">
         <v>95</v>
       </c>
-      <c r="P4" s="227"/>
-      <c r="Q4" s="231"/>
-      <c r="R4" s="231"/>
-      <c r="S4" s="227"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="230"/>
       <c r="T4" s="36"/>
-      <c r="U4" s="232" t="s">
+      <c r="U4" s="233" t="s">
         <v>96</v>
       </c>
-      <c r="V4" s="232"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="232"/>
-      <c r="Y4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="233"/>
+      <c r="X4" s="233"/>
+      <c r="Y4" s="233"/>
       <c r="Z4" s="36"/>
-      <c r="AA4" s="233" t="s">
+      <c r="AA4" s="234" t="s">
         <v>19</v>
       </c>
-      <c r="AB4" s="233"/>
-      <c r="AC4" s="233"/>
-      <c r="AD4" s="233"/>
-      <c r="AE4" s="233"/>
+      <c r="AB4" s="234"/>
+      <c r="AC4" s="234"/>
+      <c r="AD4" s="234"/>
+      <c r="AE4" s="234"/>
     </row>
     <row r="5" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="64"/>
       <c r="B5" s="36"/>
-      <c r="C5" s="228" t="s">
+      <c r="C5" s="225" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="228"/>
-      <c r="E5" s="228"/>
+      <c r="D5" s="225"/>
+      <c r="E5" s="225"/>
       <c r="F5" s="38"/>
       <c r="G5" s="38"/>
       <c r="H5" s="36"/>
-      <c r="I5" s="228" t="s">
+      <c r="I5" s="225" t="s">
         <v>93</v>
       </c>
-      <c r="J5" s="228"/>
-      <c r="K5" s="228"/>
+      <c r="J5" s="225"/>
+      <c r="K5" s="225"/>
       <c r="L5" s="38"/>
       <c r="M5" s="38"/>
       <c r="N5" s="36"/>
-      <c r="O5" s="228" t="s">
+      <c r="O5" s="225" t="s">
         <v>93</v>
       </c>
-      <c r="P5" s="228"/>
-      <c r="Q5" s="228"/>
+      <c r="P5" s="225"/>
+      <c r="Q5" s="225"/>
       <c r="R5" s="38"/>
       <c r="S5" s="38"/>
       <c r="T5" s="36"/>
-      <c r="U5" s="228" t="s">
+      <c r="U5" s="225" t="s">
         <v>93</v>
       </c>
-      <c r="V5" s="228"/>
-      <c r="W5" s="228"/>
+      <c r="V5" s="225"/>
+      <c r="W5" s="225"/>
       <c r="X5" s="38"/>
       <c r="Y5" s="38"/>
       <c r="Z5" s="36"/>
-      <c r="AA5" s="218" t="s">
+      <c r="AA5" s="215" t="s">
         <v>93</v>
       </c>
-      <c r="AB5" s="218"/>
-      <c r="AC5" s="218"/>
+      <c r="AB5" s="215"/>
+      <c r="AC5" s="215"/>
       <c r="AD5" s="38"/>
       <c r="AE5" s="38"/>
     </row>
     <row r="6" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="64"/>
       <c r="B6" s="36"/>
-      <c r="C6" s="227" t="s">
+      <c r="C6" s="230" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="227"/>
-      <c r="E6" s="227"/>
+      <c r="D6" s="230"/>
+      <c r="E6" s="230"/>
       <c r="F6" s="38"/>
       <c r="G6" s="38"/>
       <c r="H6" s="36"/>
-      <c r="I6" s="227" t="s">
+      <c r="I6" s="230" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="227"/>
-      <c r="K6" s="227"/>
+      <c r="J6" s="230"/>
+      <c r="K6" s="230"/>
       <c r="L6" s="38"/>
       <c r="M6" s="38"/>
       <c r="N6" s="36"/>
-      <c r="O6" s="227" t="s">
+      <c r="O6" s="230" t="s">
         <v>28</v>
       </c>
-      <c r="P6" s="227"/>
-      <c r="Q6" s="227"/>
+      <c r="P6" s="230"/>
+      <c r="Q6" s="230"/>
       <c r="R6" s="38"/>
       <c r="S6" s="38"/>
       <c r="T6" s="36"/>
-      <c r="U6" s="227" t="s">
+      <c r="U6" s="230" t="s">
         <v>28</v>
       </c>
-      <c r="V6" s="227"/>
-      <c r="W6" s="227"/>
+      <c r="V6" s="230"/>
+      <c r="W6" s="230"/>
       <c r="X6" s="38"/>
       <c r="Y6" s="38"/>
       <c r="Z6" s="36"/>
-      <c r="AA6" s="227" t="s">
+      <c r="AA6" s="230" t="s">
         <v>28</v>
       </c>
-      <c r="AB6" s="227"/>
-      <c r="AC6" s="227"/>
+      <c r="AB6" s="230"/>
+      <c r="AC6" s="230"/>
       <c r="AD6" s="38"/>
       <c r="AE6" s="38"/>
     </row>
@@ -10979,425 +10968,425 @@
       </c>
     </row>
     <row r="39" spans="1:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="234" t="s">
+      <c r="A39" s="231" t="s">
         <v>138</v>
       </c>
-      <c r="B39" s="234"/>
-      <c r="C39" s="234"/>
-      <c r="D39" s="234"/>
-      <c r="E39" s="234"/>
-      <c r="F39" s="234"/>
-      <c r="G39" s="234"/>
-      <c r="H39" s="234"/>
-      <c r="I39" s="234"/>
-      <c r="J39" s="234"/>
-      <c r="K39" s="234"/>
-      <c r="L39" s="234"/>
-      <c r="M39" s="234"/>
-      <c r="N39" s="234"/>
-      <c r="O39" s="234"/>
-      <c r="P39" s="234"/>
-      <c r="Q39" s="234"/>
-      <c r="R39" s="234"/>
-      <c r="S39" s="234"/>
-      <c r="T39" s="234"/>
-      <c r="U39" s="234"/>
-      <c r="V39" s="234"/>
-      <c r="W39" s="234"/>
-      <c r="X39" s="234"/>
-      <c r="Y39" s="234"/>
-      <c r="Z39" s="234"/>
-      <c r="AA39" s="234"/>
-      <c r="AB39" s="234"/>
-      <c r="AC39" s="234"/>
-      <c r="AD39" s="234"/>
-      <c r="AE39" s="234"/>
+      <c r="B39" s="231"/>
+      <c r="C39" s="231"/>
+      <c r="D39" s="231"/>
+      <c r="E39" s="231"/>
+      <c r="F39" s="231"/>
+      <c r="G39" s="231"/>
+      <c r="H39" s="231"/>
+      <c r="I39" s="231"/>
+      <c r="J39" s="231"/>
+      <c r="K39" s="231"/>
+      <c r="L39" s="231"/>
+      <c r="M39" s="231"/>
+      <c r="N39" s="231"/>
+      <c r="O39" s="231"/>
+      <c r="P39" s="231"/>
+      <c r="Q39" s="231"/>
+      <c r="R39" s="231"/>
+      <c r="S39" s="231"/>
+      <c r="T39" s="231"/>
+      <c r="U39" s="231"/>
+      <c r="V39" s="231"/>
+      <c r="W39" s="231"/>
+      <c r="X39" s="231"/>
+      <c r="Y39" s="231"/>
+      <c r="Z39" s="231"/>
+      <c r="AA39" s="231"/>
+      <c r="AB39" s="231"/>
+      <c r="AC39" s="231"/>
+      <c r="AD39" s="231"/>
+      <c r="AE39" s="231"/>
     </row>
     <row r="40" spans="1:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="215" t="s">
+      <c r="A40" s="217" t="s">
         <v>165</v>
       </c>
-      <c r="B40" s="215"/>
-      <c r="C40" s="215"/>
-      <c r="D40" s="215"/>
-      <c r="E40" s="215"/>
-      <c r="F40" s="215"/>
-      <c r="G40" s="215"/>
-      <c r="H40" s="215"/>
-      <c r="I40" s="215"/>
-      <c r="J40" s="215"/>
-      <c r="K40" s="215"/>
-      <c r="L40" s="215"/>
-      <c r="M40" s="215"/>
-      <c r="N40" s="215"/>
-      <c r="O40" s="215"/>
-      <c r="P40" s="215"/>
-      <c r="Q40" s="215"/>
-      <c r="R40" s="215"/>
-      <c r="S40" s="215"/>
-      <c r="T40" s="215"/>
-      <c r="U40" s="215"/>
-      <c r="V40" s="215"/>
-      <c r="W40" s="215"/>
-      <c r="X40" s="215"/>
-      <c r="Y40" s="215"/>
-      <c r="Z40" s="215"/>
-      <c r="AA40" s="215"/>
-      <c r="AB40" s="215"/>
-      <c r="AC40" s="215"/>
-      <c r="AD40" s="215"/>
-      <c r="AE40" s="215"/>
+      <c r="B40" s="217"/>
+      <c r="C40" s="217"/>
+      <c r="D40" s="217"/>
+      <c r="E40" s="217"/>
+      <c r="F40" s="217"/>
+      <c r="G40" s="217"/>
+      <c r="H40" s="217"/>
+      <c r="I40" s="217"/>
+      <c r="J40" s="217"/>
+      <c r="K40" s="217"/>
+      <c r="L40" s="217"/>
+      <c r="M40" s="217"/>
+      <c r="N40" s="217"/>
+      <c r="O40" s="217"/>
+      <c r="P40" s="217"/>
+      <c r="Q40" s="217"/>
+      <c r="R40" s="217"/>
+      <c r="S40" s="217"/>
+      <c r="T40" s="217"/>
+      <c r="U40" s="217"/>
+      <c r="V40" s="217"/>
+      <c r="W40" s="217"/>
+      <c r="X40" s="217"/>
+      <c r="Y40" s="217"/>
+      <c r="Z40" s="217"/>
+      <c r="AA40" s="217"/>
+      <c r="AB40" s="217"/>
+      <c r="AC40" s="217"/>
+      <c r="AD40" s="217"/>
+      <c r="AE40" s="217"/>
     </row>
     <row r="41" spans="1:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="215" t="s">
+      <c r="A41" s="217" t="s">
         <v>128</v>
       </c>
-      <c r="B41" s="215"/>
-      <c r="C41" s="215"/>
-      <c r="D41" s="215"/>
-      <c r="E41" s="215"/>
-      <c r="F41" s="215"/>
-      <c r="G41" s="215"/>
-      <c r="H41" s="215"/>
-      <c r="I41" s="215"/>
-      <c r="J41" s="215"/>
-      <c r="K41" s="215"/>
-      <c r="L41" s="215"/>
-      <c r="M41" s="215"/>
-      <c r="N41" s="215"/>
-      <c r="O41" s="215"/>
-      <c r="P41" s="215"/>
-      <c r="Q41" s="215"/>
-      <c r="R41" s="215"/>
-      <c r="S41" s="215"/>
-      <c r="T41" s="215"/>
-      <c r="U41" s="215"/>
-      <c r="V41" s="215"/>
-      <c r="W41" s="215"/>
-      <c r="X41" s="215"/>
-      <c r="Y41" s="215"/>
-      <c r="Z41" s="215"/>
-      <c r="AA41" s="215"/>
-      <c r="AB41" s="215"/>
-      <c r="AC41" s="215"/>
-      <c r="AD41" s="215"/>
-      <c r="AE41" s="215"/>
+      <c r="B41" s="217"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="217"/>
+      <c r="E41" s="217"/>
+      <c r="F41" s="217"/>
+      <c r="G41" s="217"/>
+      <c r="H41" s="217"/>
+      <c r="I41" s="217"/>
+      <c r="J41" s="217"/>
+      <c r="K41" s="217"/>
+      <c r="L41" s="217"/>
+      <c r="M41" s="217"/>
+      <c r="N41" s="217"/>
+      <c r="O41" s="217"/>
+      <c r="P41" s="217"/>
+      <c r="Q41" s="217"/>
+      <c r="R41" s="217"/>
+      <c r="S41" s="217"/>
+      <c r="T41" s="217"/>
+      <c r="U41" s="217"/>
+      <c r="V41" s="217"/>
+      <c r="W41" s="217"/>
+      <c r="X41" s="217"/>
+      <c r="Y41" s="217"/>
+      <c r="Z41" s="217"/>
+      <c r="AA41" s="217"/>
+      <c r="AB41" s="217"/>
+      <c r="AC41" s="217"/>
+      <c r="AD41" s="217"/>
+      <c r="AE41" s="217"/>
     </row>
     <row r="42" spans="1:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="215" t="s">
+      <c r="A42" s="217" t="s">
         <v>151</v>
       </c>
-      <c r="B42" s="215"/>
-      <c r="C42" s="215"/>
-      <c r="D42" s="215"/>
-      <c r="E42" s="215"/>
-      <c r="F42" s="215"/>
-      <c r="G42" s="215"/>
-      <c r="H42" s="215"/>
-      <c r="I42" s="215"/>
-      <c r="J42" s="215"/>
-      <c r="K42" s="215"/>
-      <c r="L42" s="215"/>
-      <c r="M42" s="215"/>
-      <c r="N42" s="215"/>
-      <c r="O42" s="215"/>
-      <c r="P42" s="215"/>
-      <c r="Q42" s="215"/>
-      <c r="R42" s="215"/>
-      <c r="S42" s="215"/>
-      <c r="T42" s="215"/>
-      <c r="U42" s="215"/>
-      <c r="V42" s="215"/>
-      <c r="W42" s="215"/>
-      <c r="X42" s="215"/>
-      <c r="Y42" s="215"/>
-      <c r="Z42" s="215"/>
-      <c r="AA42" s="215"/>
-      <c r="AB42" s="215"/>
-      <c r="AC42" s="215"/>
-      <c r="AD42" s="215"/>
-      <c r="AE42" s="215"/>
+      <c r="B42" s="217"/>
+      <c r="C42" s="217"/>
+      <c r="D42" s="217"/>
+      <c r="E42" s="217"/>
+      <c r="F42" s="217"/>
+      <c r="G42" s="217"/>
+      <c r="H42" s="217"/>
+      <c r="I42" s="217"/>
+      <c r="J42" s="217"/>
+      <c r="K42" s="217"/>
+      <c r="L42" s="217"/>
+      <c r="M42" s="217"/>
+      <c r="N42" s="217"/>
+      <c r="O42" s="217"/>
+      <c r="P42" s="217"/>
+      <c r="Q42" s="217"/>
+      <c r="R42" s="217"/>
+      <c r="S42" s="217"/>
+      <c r="T42" s="217"/>
+      <c r="U42" s="217"/>
+      <c r="V42" s="217"/>
+      <c r="W42" s="217"/>
+      <c r="X42" s="217"/>
+      <c r="Y42" s="217"/>
+      <c r="Z42" s="217"/>
+      <c r="AA42" s="217"/>
+      <c r="AB42" s="217"/>
+      <c r="AC42" s="217"/>
+      <c r="AD42" s="217"/>
+      <c r="AE42" s="217"/>
     </row>
     <row r="43" spans="1:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="215" t="s">
+      <c r="A43" s="217" t="s">
         <v>148</v>
       </c>
-      <c r="B43" s="215"/>
-      <c r="C43" s="215"/>
-      <c r="D43" s="215"/>
-      <c r="E43" s="215"/>
-      <c r="F43" s="215"/>
-      <c r="G43" s="215"/>
-      <c r="H43" s="215"/>
-      <c r="I43" s="215"/>
-      <c r="J43" s="215"/>
-      <c r="K43" s="215"/>
-      <c r="L43" s="215"/>
-      <c r="M43" s="215"/>
-      <c r="N43" s="215"/>
-      <c r="O43" s="215"/>
-      <c r="P43" s="215"/>
-      <c r="Q43" s="215"/>
-      <c r="R43" s="215"/>
-      <c r="S43" s="215"/>
-      <c r="T43" s="215"/>
-      <c r="U43" s="215"/>
-      <c r="V43" s="215"/>
-      <c r="W43" s="215"/>
-      <c r="X43" s="215"/>
-      <c r="Y43" s="215"/>
-      <c r="Z43" s="215"/>
-      <c r="AA43" s="215"/>
-      <c r="AB43" s="215"/>
-      <c r="AC43" s="215"/>
-      <c r="AD43" s="215"/>
-      <c r="AE43" s="215"/>
+      <c r="B43" s="217"/>
+      <c r="C43" s="217"/>
+      <c r="D43" s="217"/>
+      <c r="E43" s="217"/>
+      <c r="F43" s="217"/>
+      <c r="G43" s="217"/>
+      <c r="H43" s="217"/>
+      <c r="I43" s="217"/>
+      <c r="J43" s="217"/>
+      <c r="K43" s="217"/>
+      <c r="L43" s="217"/>
+      <c r="M43" s="217"/>
+      <c r="N43" s="217"/>
+      <c r="O43" s="217"/>
+      <c r="P43" s="217"/>
+      <c r="Q43" s="217"/>
+      <c r="R43" s="217"/>
+      <c r="S43" s="217"/>
+      <c r="T43" s="217"/>
+      <c r="U43" s="217"/>
+      <c r="V43" s="217"/>
+      <c r="W43" s="217"/>
+      <c r="X43" s="217"/>
+      <c r="Y43" s="217"/>
+      <c r="Z43" s="217"/>
+      <c r="AA43" s="217"/>
+      <c r="AB43" s="217"/>
+      <c r="AC43" s="217"/>
+      <c r="AD43" s="217"/>
+      <c r="AE43" s="217"/>
       <c r="AF43" s="82"/>
     </row>
     <row r="44" spans="1:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="215" t="s">
+      <c r="A44" s="217" t="s">
         <v>149</v>
       </c>
-      <c r="B44" s="215"/>
-      <c r="C44" s="215"/>
-      <c r="D44" s="215"/>
-      <c r="E44" s="215"/>
-      <c r="F44" s="215"/>
-      <c r="G44" s="215"/>
-      <c r="H44" s="215"/>
-      <c r="I44" s="215"/>
-      <c r="J44" s="215"/>
-      <c r="K44" s="215"/>
-      <c r="L44" s="215"/>
-      <c r="M44" s="215"/>
-      <c r="N44" s="215"/>
-      <c r="O44" s="215"/>
-      <c r="P44" s="215"/>
-      <c r="Q44" s="215"/>
-      <c r="R44" s="215"/>
-      <c r="S44" s="215"/>
-      <c r="T44" s="215"/>
-      <c r="U44" s="215"/>
-      <c r="V44" s="215"/>
-      <c r="W44" s="215"/>
-      <c r="X44" s="215"/>
-      <c r="Y44" s="215"/>
-      <c r="Z44" s="215"/>
-      <c r="AA44" s="215"/>
-      <c r="AB44" s="215"/>
-      <c r="AC44" s="215"/>
-      <c r="AD44" s="215"/>
-      <c r="AE44" s="215"/>
+      <c r="B44" s="217"/>
+      <c r="C44" s="217"/>
+      <c r="D44" s="217"/>
+      <c r="E44" s="217"/>
+      <c r="F44" s="217"/>
+      <c r="G44" s="217"/>
+      <c r="H44" s="217"/>
+      <c r="I44" s="217"/>
+      <c r="J44" s="217"/>
+      <c r="K44" s="217"/>
+      <c r="L44" s="217"/>
+      <c r="M44" s="217"/>
+      <c r="N44" s="217"/>
+      <c r="O44" s="217"/>
+      <c r="P44" s="217"/>
+      <c r="Q44" s="217"/>
+      <c r="R44" s="217"/>
+      <c r="S44" s="217"/>
+      <c r="T44" s="217"/>
+      <c r="U44" s="217"/>
+      <c r="V44" s="217"/>
+      <c r="W44" s="217"/>
+      <c r="X44" s="217"/>
+      <c r="Y44" s="217"/>
+      <c r="Z44" s="217"/>
+      <c r="AA44" s="217"/>
+      <c r="AB44" s="217"/>
+      <c r="AC44" s="217"/>
+      <c r="AD44" s="217"/>
+      <c r="AE44" s="217"/>
       <c r="AF44" s="82"/>
     </row>
     <row r="45" spans="1:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="215" t="s">
+      <c r="A45" s="217" t="s">
         <v>150</v>
       </c>
-      <c r="B45" s="215"/>
-      <c r="C45" s="215"/>
-      <c r="D45" s="215"/>
-      <c r="E45" s="215"/>
-      <c r="F45" s="215"/>
-      <c r="G45" s="215"/>
-      <c r="H45" s="215"/>
-      <c r="I45" s="215"/>
-      <c r="J45" s="215"/>
-      <c r="K45" s="215"/>
-      <c r="L45" s="215"/>
-      <c r="M45" s="215"/>
-      <c r="N45" s="215"/>
-      <c r="O45" s="215"/>
-      <c r="P45" s="215"/>
-      <c r="Q45" s="215"/>
-      <c r="R45" s="215"/>
-      <c r="S45" s="215"/>
-      <c r="T45" s="215"/>
-      <c r="U45" s="215"/>
-      <c r="V45" s="215"/>
-      <c r="W45" s="215"/>
-      <c r="X45" s="215"/>
-      <c r="Y45" s="215"/>
-      <c r="Z45" s="215"/>
-      <c r="AA45" s="215"/>
-      <c r="AB45" s="215"/>
-      <c r="AC45" s="215"/>
-      <c r="AD45" s="215"/>
-      <c r="AE45" s="215"/>
+      <c r="B45" s="217"/>
+      <c r="C45" s="217"/>
+      <c r="D45" s="217"/>
+      <c r="E45" s="217"/>
+      <c r="F45" s="217"/>
+      <c r="G45" s="217"/>
+      <c r="H45" s="217"/>
+      <c r="I45" s="217"/>
+      <c r="J45" s="217"/>
+      <c r="K45" s="217"/>
+      <c r="L45" s="217"/>
+      <c r="M45" s="217"/>
+      <c r="N45" s="217"/>
+      <c r="O45" s="217"/>
+      <c r="P45" s="217"/>
+      <c r="Q45" s="217"/>
+      <c r="R45" s="217"/>
+      <c r="S45" s="217"/>
+      <c r="T45" s="217"/>
+      <c r="U45" s="217"/>
+      <c r="V45" s="217"/>
+      <c r="W45" s="217"/>
+      <c r="X45" s="217"/>
+      <c r="Y45" s="217"/>
+      <c r="Z45" s="217"/>
+      <c r="AA45" s="217"/>
+      <c r="AB45" s="217"/>
+      <c r="AC45" s="217"/>
+      <c r="AD45" s="217"/>
+      <c r="AE45" s="217"/>
       <c r="AF45" s="82"/>
     </row>
     <row r="46" spans="1:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="215" t="s">
+      <c r="A46" s="217" t="s">
         <v>129</v>
       </c>
-      <c r="B46" s="215"/>
-      <c r="C46" s="215"/>
-      <c r="D46" s="215"/>
-      <c r="E46" s="215"/>
-      <c r="F46" s="215"/>
-      <c r="G46" s="215"/>
-      <c r="H46" s="215"/>
-      <c r="I46" s="215"/>
-      <c r="J46" s="215"/>
-      <c r="K46" s="215"/>
-      <c r="L46" s="215"/>
-      <c r="M46" s="215"/>
-      <c r="N46" s="215"/>
-      <c r="O46" s="215"/>
-      <c r="P46" s="215"/>
-      <c r="Q46" s="215"/>
-      <c r="R46" s="215"/>
-      <c r="S46" s="215"/>
-      <c r="T46" s="215"/>
-      <c r="U46" s="215"/>
-      <c r="V46" s="215"/>
-      <c r="W46" s="215"/>
-      <c r="X46" s="215"/>
-      <c r="Y46" s="215"/>
-      <c r="Z46" s="215"/>
-      <c r="AA46" s="215"/>
-      <c r="AB46" s="215"/>
-      <c r="AC46" s="215"/>
-      <c r="AD46" s="215"/>
-      <c r="AE46" s="215"/>
+      <c r="B46" s="217"/>
+      <c r="C46" s="217"/>
+      <c r="D46" s="217"/>
+      <c r="E46" s="217"/>
+      <c r="F46" s="217"/>
+      <c r="G46" s="217"/>
+      <c r="H46" s="217"/>
+      <c r="I46" s="217"/>
+      <c r="J46" s="217"/>
+      <c r="K46" s="217"/>
+      <c r="L46" s="217"/>
+      <c r="M46" s="217"/>
+      <c r="N46" s="217"/>
+      <c r="O46" s="217"/>
+      <c r="P46" s="217"/>
+      <c r="Q46" s="217"/>
+      <c r="R46" s="217"/>
+      <c r="S46" s="217"/>
+      <c r="T46" s="217"/>
+      <c r="U46" s="217"/>
+      <c r="V46" s="217"/>
+      <c r="W46" s="217"/>
+      <c r="X46" s="217"/>
+      <c r="Y46" s="217"/>
+      <c r="Z46" s="217"/>
+      <c r="AA46" s="217"/>
+      <c r="AB46" s="217"/>
+      <c r="AC46" s="217"/>
+      <c r="AD46" s="217"/>
+      <c r="AE46" s="217"/>
     </row>
     <row r="47" spans="1:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="215" t="s">
+      <c r="A47" s="217" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="215"/>
-      <c r="C47" s="215"/>
-      <c r="D47" s="215"/>
-      <c r="E47" s="215"/>
-      <c r="F47" s="215"/>
-      <c r="G47" s="215"/>
-      <c r="H47" s="215"/>
-      <c r="I47" s="215"/>
-      <c r="J47" s="215"/>
-      <c r="K47" s="215"/>
-      <c r="L47" s="215"/>
-      <c r="M47" s="215"/>
-      <c r="N47" s="215"/>
-      <c r="O47" s="215"/>
-      <c r="P47" s="215"/>
-      <c r="Q47" s="215"/>
-      <c r="R47" s="215"/>
-      <c r="S47" s="215"/>
-      <c r="T47" s="215"/>
-      <c r="U47" s="215"/>
-      <c r="V47" s="215"/>
-      <c r="W47" s="215"/>
-      <c r="X47" s="215"/>
-      <c r="Y47" s="215"/>
-      <c r="Z47" s="215"/>
-      <c r="AA47" s="215"/>
-      <c r="AB47" s="215"/>
-      <c r="AC47" s="215"/>
-      <c r="AD47" s="215"/>
-      <c r="AE47" s="215"/>
+      <c r="B47" s="217"/>
+      <c r="C47" s="217"/>
+      <c r="D47" s="217"/>
+      <c r="E47" s="217"/>
+      <c r="F47" s="217"/>
+      <c r="G47" s="217"/>
+      <c r="H47" s="217"/>
+      <c r="I47" s="217"/>
+      <c r="J47" s="217"/>
+      <c r="K47" s="217"/>
+      <c r="L47" s="217"/>
+      <c r="M47" s="217"/>
+      <c r="N47" s="217"/>
+      <c r="O47" s="217"/>
+      <c r="P47" s="217"/>
+      <c r="Q47" s="217"/>
+      <c r="R47" s="217"/>
+      <c r="S47" s="217"/>
+      <c r="T47" s="217"/>
+      <c r="U47" s="217"/>
+      <c r="V47" s="217"/>
+      <c r="W47" s="217"/>
+      <c r="X47" s="217"/>
+      <c r="Y47" s="217"/>
+      <c r="Z47" s="217"/>
+      <c r="AA47" s="217"/>
+      <c r="AB47" s="217"/>
+      <c r="AC47" s="217"/>
+      <c r="AD47" s="217"/>
+      <c r="AE47" s="217"/>
     </row>
     <row r="48" spans="1:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="215" t="s">
+      <c r="A48" s="217" t="s">
         <v>131</v>
       </c>
-      <c r="B48" s="215"/>
-      <c r="C48" s="215"/>
-      <c r="D48" s="215"/>
-      <c r="E48" s="215"/>
-      <c r="F48" s="215"/>
-      <c r="G48" s="215"/>
-      <c r="H48" s="215"/>
-      <c r="I48" s="215"/>
-      <c r="J48" s="215"/>
-      <c r="K48" s="215"/>
-      <c r="L48" s="215"/>
-      <c r="M48" s="215"/>
-      <c r="N48" s="215"/>
-      <c r="O48" s="215"/>
-      <c r="P48" s="215"/>
-      <c r="Q48" s="215"/>
-      <c r="R48" s="215"/>
-      <c r="S48" s="215"/>
-      <c r="T48" s="215"/>
-      <c r="U48" s="215"/>
-      <c r="V48" s="215"/>
-      <c r="W48" s="215"/>
-      <c r="X48" s="215"/>
-      <c r="Y48" s="215"/>
-      <c r="Z48" s="215"/>
-      <c r="AA48" s="215"/>
-      <c r="AB48" s="215"/>
-      <c r="AC48" s="215"/>
-      <c r="AD48" s="215"/>
-      <c r="AE48" s="215"/>
+      <c r="B48" s="217"/>
+      <c r="C48" s="217"/>
+      <c r="D48" s="217"/>
+      <c r="E48" s="217"/>
+      <c r="F48" s="217"/>
+      <c r="G48" s="217"/>
+      <c r="H48" s="217"/>
+      <c r="I48" s="217"/>
+      <c r="J48" s="217"/>
+      <c r="K48" s="217"/>
+      <c r="L48" s="217"/>
+      <c r="M48" s="217"/>
+      <c r="N48" s="217"/>
+      <c r="O48" s="217"/>
+      <c r="P48" s="217"/>
+      <c r="Q48" s="217"/>
+      <c r="R48" s="217"/>
+      <c r="S48" s="217"/>
+      <c r="T48" s="217"/>
+      <c r="U48" s="217"/>
+      <c r="V48" s="217"/>
+      <c r="W48" s="217"/>
+      <c r="X48" s="217"/>
+      <c r="Y48" s="217"/>
+      <c r="Z48" s="217"/>
+      <c r="AA48" s="217"/>
+      <c r="AB48" s="217"/>
+      <c r="AC48" s="217"/>
+      <c r="AD48" s="217"/>
+      <c r="AE48" s="217"/>
     </row>
     <row r="49" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="215"/>
-      <c r="B49" s="215"/>
-      <c r="C49" s="215"/>
-      <c r="D49" s="215"/>
-      <c r="E49" s="215"/>
-      <c r="F49" s="215"/>
-      <c r="G49" s="215"/>
-      <c r="H49" s="215"/>
-      <c r="I49" s="215"/>
-      <c r="J49" s="215"/>
-      <c r="K49" s="215"/>
-      <c r="L49" s="215"/>
-      <c r="M49" s="215"/>
-      <c r="N49" s="215"/>
-      <c r="O49" s="215"/>
-      <c r="P49" s="215"/>
-      <c r="Q49" s="215"/>
-      <c r="R49" s="215"/>
-      <c r="S49" s="215"/>
-      <c r="T49" s="215"/>
-      <c r="U49" s="215"/>
-      <c r="V49" s="215"/>
-      <c r="W49" s="215"/>
-      <c r="X49" s="215"/>
-      <c r="Y49" s="215"/>
-      <c r="Z49" s="215"/>
-      <c r="AA49" s="215"/>
-      <c r="AB49" s="215"/>
-      <c r="AC49" s="215"/>
-      <c r="AD49" s="215"/>
-      <c r="AE49" s="215"/>
+      <c r="A49" s="217"/>
+      <c r="B49" s="217"/>
+      <c r="C49" s="217"/>
+      <c r="D49" s="217"/>
+      <c r="E49" s="217"/>
+      <c r="F49" s="217"/>
+      <c r="G49" s="217"/>
+      <c r="H49" s="217"/>
+      <c r="I49" s="217"/>
+      <c r="J49" s="217"/>
+      <c r="K49" s="217"/>
+      <c r="L49" s="217"/>
+      <c r="M49" s="217"/>
+      <c r="N49" s="217"/>
+      <c r="O49" s="217"/>
+      <c r="P49" s="217"/>
+      <c r="Q49" s="217"/>
+      <c r="R49" s="217"/>
+      <c r="S49" s="217"/>
+      <c r="T49" s="217"/>
+      <c r="U49" s="217"/>
+      <c r="V49" s="217"/>
+      <c r="W49" s="217"/>
+      <c r="X49" s="217"/>
+      <c r="Y49" s="217"/>
+      <c r="Z49" s="217"/>
+      <c r="AA49" s="217"/>
+      <c r="AB49" s="217"/>
+      <c r="AC49" s="217"/>
+      <c r="AD49" s="217"/>
+      <c r="AE49" s="217"/>
     </row>
     <row r="50" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="215" t="s">
+      <c r="A50" s="217" t="s">
         <v>37</v>
       </c>
-      <c r="B50" s="215"/>
-      <c r="C50" s="215"/>
-      <c r="D50" s="215"/>
-      <c r="E50" s="215"/>
-      <c r="F50" s="215"/>
-      <c r="G50" s="215"/>
-      <c r="H50" s="215"/>
-      <c r="I50" s="215"/>
-      <c r="J50" s="215"/>
-      <c r="K50" s="215"/>
-      <c r="L50" s="215"/>
-      <c r="M50" s="215"/>
-      <c r="N50" s="215"/>
-      <c r="O50" s="215"/>
-      <c r="P50" s="215"/>
-      <c r="Q50" s="215"/>
-      <c r="R50" s="215"/>
-      <c r="S50" s="215"/>
-      <c r="T50" s="215"/>
-      <c r="U50" s="215"/>
-      <c r="V50" s="215"/>
-      <c r="W50" s="215"/>
-      <c r="X50" s="215"/>
-      <c r="Y50" s="215"/>
-      <c r="Z50" s="215"/>
-      <c r="AA50" s="215"/>
-      <c r="AB50" s="215"/>
-      <c r="AC50" s="215"/>
-      <c r="AD50" s="215"/>
-      <c r="AE50" s="215"/>
+      <c r="B50" s="217"/>
+      <c r="C50" s="217"/>
+      <c r="D50" s="217"/>
+      <c r="E50" s="217"/>
+      <c r="F50" s="217"/>
+      <c r="G50" s="217"/>
+      <c r="H50" s="217"/>
+      <c r="I50" s="217"/>
+      <c r="J50" s="217"/>
+      <c r="K50" s="217"/>
+      <c r="L50" s="217"/>
+      <c r="M50" s="217"/>
+      <c r="N50" s="217"/>
+      <c r="O50" s="217"/>
+      <c r="P50" s="217"/>
+      <c r="Q50" s="217"/>
+      <c r="R50" s="217"/>
+      <c r="S50" s="217"/>
+      <c r="T50" s="217"/>
+      <c r="U50" s="217"/>
+      <c r="V50" s="217"/>
+      <c r="W50" s="217"/>
+      <c r="X50" s="217"/>
+      <c r="Y50" s="217"/>
+      <c r="Z50" s="217"/>
+      <c r="AA50" s="217"/>
+      <c r="AB50" s="217"/>
+      <c r="AC50" s="217"/>
+      <c r="AD50" s="217"/>
+      <c r="AE50" s="217"/>
     </row>
     <row r="51" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C51" s="22"/>
@@ -11660,20 +11649,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="AA5:AC5"/>
-    <mergeCell ref="AA6:AC6"/>
-    <mergeCell ref="A50:AE50"/>
-    <mergeCell ref="A39:AE39"/>
-    <mergeCell ref="A40:AE40"/>
-    <mergeCell ref="A41:AE41"/>
-    <mergeCell ref="A42:AE42"/>
-    <mergeCell ref="A43:AE43"/>
-    <mergeCell ref="A44:AE44"/>
-    <mergeCell ref="A45:AE45"/>
-    <mergeCell ref="A46:AE46"/>
-    <mergeCell ref="A47:AE47"/>
-    <mergeCell ref="A48:AE48"/>
-    <mergeCell ref="A49:AE49"/>
     <mergeCell ref="A1:AE1"/>
     <mergeCell ref="A2:AE2"/>
     <mergeCell ref="A3:AE3"/>
@@ -11690,6 +11665,20 @@
     <mergeCell ref="AA4:AE4"/>
     <mergeCell ref="U5:W5"/>
     <mergeCell ref="U6:W6"/>
+    <mergeCell ref="AA5:AC5"/>
+    <mergeCell ref="AA6:AC6"/>
+    <mergeCell ref="A50:AE50"/>
+    <mergeCell ref="A39:AE39"/>
+    <mergeCell ref="A40:AE40"/>
+    <mergeCell ref="A41:AE41"/>
+    <mergeCell ref="A42:AE42"/>
+    <mergeCell ref="A43:AE43"/>
+    <mergeCell ref="A44:AE44"/>
+    <mergeCell ref="A45:AE45"/>
+    <mergeCell ref="A46:AE46"/>
+    <mergeCell ref="A47:AE47"/>
+    <mergeCell ref="A48:AE48"/>
+    <mergeCell ref="A49:AE49"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup scale="63" orientation="portrait" r:id="rId1"/>
@@ -11708,48 +11697,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="218" t="s">
+      <c r="A1" s="215" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="218"/>
-      <c r="C1" s="218"/>
-      <c r="D1" s="218"/>
+      <c r="B1" s="215"/>
+      <c r="C1" s="215"/>
+      <c r="D1" s="215"/>
     </row>
     <row r="2" spans="1:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="218" t="s">
+      <c r="A2" s="215" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="218"/>
-      <c r="C2" s="218"/>
-      <c r="D2" s="218"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
     </row>
     <row r="3" spans="1:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="218" t="s">
+      <c r="A3" s="215" t="s">
         <v>154</v>
       </c>
-      <c r="B3" s="218"/>
-      <c r="C3" s="218"/>
-      <c r="D3" s="218"/>
+      <c r="B3" s="215"/>
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
     </row>
     <row r="4" spans="1:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="218"/>
-      <c r="B4" s="218"/>
-      <c r="C4" s="218"/>
-      <c r="D4" s="218"/>
+      <c r="A4" s="215"/>
+      <c r="B4" s="215"/>
+      <c r="C4" s="215"/>
+      <c r="D4" s="215"/>
     </row>
     <row r="5" spans="1:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="218" t="s">
+      <c r="A5" s="215" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="218"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="218"/>
+      <c r="B5" s="215"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="215"/>
     </row>
     <row r="6" spans="1:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="218"/>
-      <c r="B6" s="218"/>
-      <c r="C6" s="218"/>
-      <c r="D6" s="218"/>
+      <c r="A6" s="215"/>
+      <c r="B6" s="215"/>
+      <c r="C6" s="215"/>
+      <c r="D6" s="215"/>
     </row>
     <row r="7" spans="1:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="35" t="s">
@@ -12000,28 +11989,28 @@
       <c r="D29" s="109"/>
     </row>
     <row r="30" spans="1:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="215" t="s">
+      <c r="A30" s="217" t="s">
         <v>132</v>
       </c>
-      <c r="B30" s="215"/>
-      <c r="C30" s="215"/>
-      <c r="D30" s="215"/>
+      <c r="B30" s="217"/>
+      <c r="C30" s="217"/>
+      <c r="D30" s="217"/>
     </row>
     <row r="31" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="216" t="s">
+      <c r="A31" s="218" t="s">
         <v>166</v>
       </c>
-      <c r="B31" s="216"/>
-      <c r="C31" s="216"/>
-      <c r="D31" s="216"/>
+      <c r="B31" s="218"/>
+      <c r="C31" s="218"/>
+      <c r="D31" s="218"/>
     </row>
     <row r="32" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="216" t="s">
+      <c r="A32" s="218" t="s">
         <v>133</v>
       </c>
-      <c r="B32" s="216"/>
-      <c r="C32" s="216"/>
-      <c r="D32" s="216"/>
+      <c r="B32" s="218"/>
+      <c r="C32" s="218"/>
+      <c r="D32" s="218"/>
     </row>
     <row r="33" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="236" t="s">
@@ -12041,17 +12030,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A32:D32"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -12079,80 +12068,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="238" t="s">
+      <c r="A1" s="239" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="238"/>
-      <c r="C1" s="238"/>
-      <c r="D1" s="238"/>
-      <c r="E1" s="238"/>
-      <c r="F1" s="238"/>
-      <c r="G1" s="238"/>
-      <c r="H1" s="238"/>
-      <c r="I1" s="238"/>
-      <c r="J1" s="238"/>
-      <c r="K1" s="238"/>
-      <c r="L1" s="238"/>
+      <c r="B1" s="239"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="239"/>
+      <c r="L1" s="239"/>
     </row>
     <row r="2" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="238" t="s">
+      <c r="A2" s="239" t="s">
         <v>208</v>
       </c>
-      <c r="B2" s="238"/>
-      <c r="C2" s="238"/>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="238"/>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="B2" s="239"/>
+      <c r="C2" s="239"/>
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="239"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="239"/>
+      <c r="I2" s="239"/>
+      <c r="J2" s="239"/>
+      <c r="K2" s="239"/>
+      <c r="L2" s="239"/>
     </row>
     <row r="3" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="239"/>
-      <c r="B3" s="239"/>
-      <c r="C3" s="239"/>
-      <c r="D3" s="239"/>
-      <c r="E3" s="239"/>
-      <c r="F3" s="239"/>
-      <c r="G3" s="239"/>
-      <c r="H3" s="239"/>
-      <c r="I3" s="239"/>
-      <c r="J3" s="239"/>
-      <c r="K3" s="239"/>
-      <c r="L3" s="239"/>
+      <c r="A3" s="240"/>
+      <c r="B3" s="240"/>
+      <c r="C3" s="240"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
+      <c r="G3" s="240"/>
+      <c r="H3" s="240"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
     </row>
     <row r="4" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="238" t="s">
+      <c r="A4" s="239" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="238"/>
-      <c r="C4" s="238"/>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="238"/>
-      <c r="L4" s="238"/>
+      <c r="B4" s="239"/>
+      <c r="C4" s="239"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="239"/>
+      <c r="I4" s="239"/>
+      <c r="J4" s="239"/>
+      <c r="K4" s="239"/>
+      <c r="L4" s="239"/>
     </row>
     <row r="5" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="240"/>
-      <c r="B5" s="240"/>
-      <c r="C5" s="240"/>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
+      <c r="A5" s="241"/>
+      <c r="B5" s="241"/>
+      <c r="C5" s="241"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
     </row>
     <row r="6" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="167" t="s">
@@ -12828,272 +12817,263 @@
       <c r="L27" s="168"/>
     </row>
     <row r="28" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="241" t="s">
+      <c r="A28" s="242" t="s">
         <v>225</v>
       </c>
-      <c r="B28" s="242"/>
-      <c r="C28" s="242"/>
-      <c r="D28" s="242"/>
-      <c r="E28" s="242"/>
-      <c r="F28" s="242"/>
-      <c r="G28" s="242"/>
-      <c r="H28" s="242"/>
-      <c r="I28" s="242"/>
-      <c r="J28" s="242"/>
-      <c r="K28" s="242"/>
-      <c r="L28" s="242"/>
+      <c r="B28" s="243"/>
+      <c r="C28" s="243"/>
+      <c r="D28" s="243"/>
+      <c r="E28" s="243"/>
+      <c r="F28" s="243"/>
+      <c r="G28" s="243"/>
+      <c r="H28" s="243"/>
+      <c r="I28" s="243"/>
+      <c r="J28" s="243"/>
+      <c r="K28" s="243"/>
+      <c r="L28" s="243"/>
     </row>
     <row r="29" spans="1:12" s="180" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="237" t="s">
+      <c r="A29" s="238" t="s">
         <v>226</v>
       </c>
-      <c r="B29" s="237"/>
-      <c r="C29" s="237"/>
-      <c r="D29" s="237"/>
-      <c r="E29" s="237"/>
-      <c r="F29" s="237"/>
-      <c r="G29" s="237"/>
-      <c r="H29" s="237"/>
-      <c r="I29" s="237"/>
-      <c r="J29" s="237"/>
-      <c r="K29" s="237"/>
-      <c r="L29" s="237"/>
+      <c r="B29" s="238"/>
+      <c r="C29" s="238"/>
+      <c r="D29" s="238"/>
+      <c r="E29" s="238"/>
+      <c r="F29" s="238"/>
+      <c r="G29" s="238"/>
+      <c r="H29" s="238"/>
+      <c r="I29" s="238"/>
+      <c r="J29" s="238"/>
+      <c r="K29" s="238"/>
+      <c r="L29" s="238"/>
     </row>
     <row r="30" spans="1:12" s="180" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="243" t="s">
+      <c r="A30" s="244" t="s">
+        <v>257</v>
+      </c>
+      <c r="B30" s="245"/>
+      <c r="C30" s="245"/>
+      <c r="D30" s="245"/>
+      <c r="E30" s="245"/>
+      <c r="F30" s="245"/>
+      <c r="G30" s="245"/>
+      <c r="H30" s="245"/>
+      <c r="I30" s="245"/>
+      <c r="J30" s="245"/>
+      <c r="K30" s="245"/>
+      <c r="L30" s="245"/>
+    </row>
+    <row r="31" spans="1:12" s="180" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="244" t="s">
         <v>227</v>
       </c>
-      <c r="B30" s="244"/>
-      <c r="C30" s="244"/>
-      <c r="D30" s="244"/>
-      <c r="E30" s="244"/>
-      <c r="F30" s="244"/>
-      <c r="G30" s="244"/>
-      <c r="H30" s="244"/>
-      <c r="I30" s="244"/>
-      <c r="J30" s="244"/>
-      <c r="K30" s="244"/>
-      <c r="L30" s="244"/>
-    </row>
-    <row r="31" spans="1:12" s="180" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="243" t="s">
+      <c r="B31" s="245"/>
+      <c r="C31" s="245"/>
+      <c r="D31" s="245"/>
+      <c r="E31" s="245"/>
+      <c r="F31" s="245"/>
+      <c r="G31" s="245"/>
+      <c r="H31" s="245"/>
+      <c r="I31" s="245"/>
+      <c r="J31" s="245"/>
+      <c r="K31" s="245"/>
+      <c r="L31" s="245"/>
+    </row>
+    <row r="32" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="237" t="s">
         <v>228</v>
       </c>
-      <c r="B31" s="244"/>
-      <c r="C31" s="244"/>
-      <c r="D31" s="244"/>
-      <c r="E31" s="244"/>
-      <c r="F31" s="244"/>
-      <c r="G31" s="244"/>
-      <c r="H31" s="244"/>
-      <c r="I31" s="244"/>
-      <c r="J31" s="244"/>
-      <c r="K31" s="244"/>
-      <c r="L31" s="244"/>
-    </row>
-    <row r="32" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="245" t="s">
+      <c r="B32" s="237"/>
+      <c r="C32" s="237"/>
+      <c r="D32" s="237"/>
+      <c r="E32" s="237"/>
+      <c r="F32" s="237"/>
+      <c r="G32" s="237"/>
+      <c r="H32" s="237"/>
+      <c r="I32" s="237"/>
+      <c r="J32" s="237"/>
+      <c r="K32" s="237"/>
+      <c r="L32" s="237"/>
+    </row>
+    <row r="33" spans="1:12" s="180" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="238" t="s">
         <v>229</v>
       </c>
-      <c r="B32" s="245"/>
-      <c r="C32" s="245"/>
-      <c r="D32" s="245"/>
-      <c r="E32" s="245"/>
-      <c r="F32" s="245"/>
-      <c r="G32" s="245"/>
-      <c r="H32" s="245"/>
-      <c r="I32" s="245"/>
-      <c r="J32" s="245"/>
-      <c r="K32" s="245"/>
-      <c r="L32" s="245"/>
-    </row>
-    <row r="33" spans="1:12" s="180" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="237" t="s">
+      <c r="B33" s="238"/>
+      <c r="C33" s="238"/>
+      <c r="D33" s="238"/>
+      <c r="E33" s="238"/>
+      <c r="F33" s="238"/>
+      <c r="G33" s="238"/>
+      <c r="H33" s="238"/>
+      <c r="I33" s="238"/>
+      <c r="J33" s="238"/>
+      <c r="K33" s="238"/>
+      <c r="L33" s="238"/>
+    </row>
+    <row r="34" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="238" t="s">
         <v>230</v>
       </c>
-      <c r="B33" s="237"/>
-      <c r="C33" s="237"/>
-      <c r="D33" s="237"/>
-      <c r="E33" s="237"/>
-      <c r="F33" s="237"/>
-      <c r="G33" s="237"/>
-      <c r="H33" s="237"/>
-      <c r="I33" s="237"/>
-      <c r="J33" s="237"/>
-      <c r="K33" s="237"/>
-      <c r="L33" s="237"/>
-    </row>
-    <row r="34" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="237" t="s">
+      <c r="B34" s="238"/>
+      <c r="C34" s="238"/>
+      <c r="D34" s="238"/>
+      <c r="E34" s="238"/>
+      <c r="F34" s="238"/>
+      <c r="G34" s="238"/>
+      <c r="H34" s="238"/>
+      <c r="I34" s="238"/>
+      <c r="J34" s="238"/>
+      <c r="K34" s="238"/>
+      <c r="L34" s="238"/>
+    </row>
+    <row r="35" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="238" t="s">
         <v>231</v>
       </c>
-      <c r="B34" s="237"/>
-      <c r="C34" s="237"/>
-      <c r="D34" s="237"/>
-      <c r="E34" s="237"/>
-      <c r="F34" s="237"/>
-      <c r="G34" s="237"/>
-      <c r="H34" s="237"/>
-      <c r="I34" s="237"/>
-      <c r="J34" s="237"/>
-      <c r="K34" s="237"/>
-      <c r="L34" s="237"/>
-    </row>
-    <row r="35" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="237" t="s">
+      <c r="B35" s="238"/>
+      <c r="C35" s="238"/>
+      <c r="D35" s="238"/>
+      <c r="E35" s="238"/>
+      <c r="F35" s="238"/>
+      <c r="G35" s="238"/>
+      <c r="H35" s="238"/>
+      <c r="I35" s="238"/>
+      <c r="J35" s="238"/>
+      <c r="K35" s="238"/>
+      <c r="L35" s="238"/>
+    </row>
+    <row r="36" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="237" t="s">
         <v>232</v>
       </c>
-      <c r="B35" s="237"/>
-      <c r="C35" s="237"/>
-      <c r="D35" s="237"/>
-      <c r="E35" s="237"/>
-      <c r="F35" s="237"/>
-      <c r="G35" s="237"/>
-      <c r="H35" s="237"/>
-      <c r="I35" s="237"/>
-      <c r="J35" s="237"/>
-      <c r="K35" s="237"/>
-      <c r="L35" s="237"/>
-    </row>
-    <row r="36" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="245" t="s">
+      <c r="B36" s="237"/>
+      <c r="C36" s="237"/>
+      <c r="D36" s="237"/>
+      <c r="E36" s="237"/>
+      <c r="F36" s="237"/>
+      <c r="G36" s="237"/>
+      <c r="H36" s="237"/>
+      <c r="I36" s="237"/>
+      <c r="J36" s="237"/>
+      <c r="K36" s="237"/>
+      <c r="L36" s="237"/>
+    </row>
+    <row r="37" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="238" t="s">
         <v>233</v>
       </c>
-      <c r="B36" s="245"/>
-      <c r="C36" s="245"/>
-      <c r="D36" s="245"/>
-      <c r="E36" s="245"/>
-      <c r="F36" s="245"/>
-      <c r="G36" s="245"/>
-      <c r="H36" s="245"/>
-      <c r="I36" s="245"/>
-      <c r="J36" s="245"/>
-      <c r="K36" s="245"/>
-      <c r="L36" s="245"/>
-    </row>
-    <row r="37" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="237" t="s">
+      <c r="B37" s="238"/>
+      <c r="C37" s="238"/>
+      <c r="D37" s="238"/>
+      <c r="E37" s="238"/>
+      <c r="F37" s="238"/>
+      <c r="G37" s="238"/>
+      <c r="H37" s="238"/>
+      <c r="I37" s="238"/>
+      <c r="J37" s="238"/>
+      <c r="K37" s="238"/>
+      <c r="L37" s="238"/>
+    </row>
+    <row r="38" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="237" t="s">
         <v>234</v>
       </c>
-      <c r="B37" s="237"/>
-      <c r="C37" s="237"/>
-      <c r="D37" s="237"/>
-      <c r="E37" s="237"/>
-      <c r="F37" s="237"/>
-      <c r="G37" s="237"/>
-      <c r="H37" s="237"/>
-      <c r="I37" s="237"/>
-      <c r="J37" s="237"/>
-      <c r="K37" s="237"/>
-      <c r="L37" s="237"/>
-    </row>
-    <row r="38" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="245" t="s">
+      <c r="B38" s="237"/>
+      <c r="C38" s="237"/>
+      <c r="D38" s="237"/>
+      <c r="E38" s="237"/>
+      <c r="F38" s="237"/>
+      <c r="G38" s="237"/>
+      <c r="H38" s="237"/>
+      <c r="I38" s="237"/>
+      <c r="J38" s="237"/>
+      <c r="K38" s="237"/>
+      <c r="L38" s="237"/>
+    </row>
+    <row r="39" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="237" t="s">
         <v>235</v>
       </c>
-      <c r="B38" s="245"/>
-      <c r="C38" s="245"/>
-      <c r="D38" s="245"/>
-      <c r="E38" s="245"/>
-      <c r="F38" s="245"/>
-      <c r="G38" s="245"/>
-      <c r="H38" s="245"/>
-      <c r="I38" s="245"/>
-      <c r="J38" s="245"/>
-      <c r="K38" s="245"/>
-      <c r="L38" s="245"/>
-    </row>
-    <row r="39" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="245" t="s">
+      <c r="B39" s="237"/>
+      <c r="C39" s="237"/>
+      <c r="D39" s="237"/>
+      <c r="E39" s="237"/>
+      <c r="F39" s="237"/>
+      <c r="G39" s="237"/>
+      <c r="H39" s="237"/>
+      <c r="I39" s="237"/>
+      <c r="J39" s="237"/>
+      <c r="K39" s="237"/>
+      <c r="L39" s="237"/>
+    </row>
+    <row r="40" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="237" t="s">
         <v>236</v>
       </c>
-      <c r="B39" s="245"/>
-      <c r="C39" s="245"/>
-      <c r="D39" s="245"/>
-      <c r="E39" s="245"/>
-      <c r="F39" s="245"/>
-      <c r="G39" s="245"/>
-      <c r="H39" s="245"/>
-      <c r="I39" s="245"/>
-      <c r="J39" s="245"/>
-      <c r="K39" s="245"/>
-      <c r="L39" s="245"/>
-    </row>
-    <row r="40" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="245" t="s">
+      <c r="B40" s="237"/>
+      <c r="C40" s="237"/>
+      <c r="D40" s="237"/>
+      <c r="E40" s="237"/>
+      <c r="F40" s="237"/>
+      <c r="G40" s="237"/>
+      <c r="H40" s="237"/>
+      <c r="I40" s="237"/>
+      <c r="J40" s="237"/>
+      <c r="K40" s="237"/>
+      <c r="L40" s="237"/>
+    </row>
+    <row r="41" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="237" t="s">
         <v>237</v>
       </c>
-      <c r="B40" s="245"/>
-      <c r="C40" s="245"/>
-      <c r="D40" s="245"/>
-      <c r="E40" s="245"/>
-      <c r="F40" s="245"/>
-      <c r="G40" s="245"/>
-      <c r="H40" s="245"/>
-      <c r="I40" s="245"/>
-      <c r="J40" s="245"/>
-      <c r="K40" s="245"/>
-      <c r="L40" s="245"/>
-    </row>
-    <row r="41" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="245" t="s">
+      <c r="B41" s="237"/>
+      <c r="C41" s="237"/>
+      <c r="D41" s="237"/>
+      <c r="E41" s="237"/>
+      <c r="F41" s="237"/>
+      <c r="G41" s="237"/>
+      <c r="H41" s="237"/>
+      <c r="I41" s="237"/>
+      <c r="J41" s="237"/>
+      <c r="K41" s="237"/>
+      <c r="L41" s="237"/>
+    </row>
+    <row r="42" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="237" t="s">
         <v>238</v>
       </c>
-      <c r="B41" s="245"/>
-      <c r="C41" s="245"/>
-      <c r="D41" s="245"/>
-      <c r="E41" s="245"/>
-      <c r="F41" s="245"/>
-      <c r="G41" s="245"/>
-      <c r="H41" s="245"/>
-      <c r="I41" s="245"/>
-      <c r="J41" s="245"/>
-      <c r="K41" s="245"/>
-      <c r="L41" s="245"/>
-    </row>
-    <row r="42" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="245" t="s">
+      <c r="B42" s="237"/>
+      <c r="C42" s="237"/>
+      <c r="D42" s="237"/>
+      <c r="E42" s="237"/>
+      <c r="F42" s="237"/>
+      <c r="G42" s="237"/>
+      <c r="H42" s="237"/>
+      <c r="I42" s="237"/>
+      <c r="J42" s="237"/>
+      <c r="K42" s="237"/>
+      <c r="L42" s="237"/>
+    </row>
+    <row r="43" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="237" t="s">
         <v>239</v>
       </c>
-      <c r="B42" s="245"/>
-      <c r="C42" s="245"/>
-      <c r="D42" s="245"/>
-      <c r="E42" s="245"/>
-      <c r="F42" s="245"/>
-      <c r="G42" s="245"/>
-      <c r="H42" s="245"/>
-      <c r="I42" s="245"/>
-      <c r="J42" s="245"/>
-      <c r="K42" s="245"/>
-      <c r="L42" s="245"/>
-    </row>
-    <row r="43" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="245" t="s">
-        <v>240</v>
-      </c>
-      <c r="B43" s="245"/>
-      <c r="C43" s="245"/>
-      <c r="D43" s="245"/>
-      <c r="E43" s="245"/>
-      <c r="F43" s="245"/>
-      <c r="G43" s="245"/>
-      <c r="H43" s="245"/>
-      <c r="I43" s="245"/>
-      <c r="J43" s="245"/>
-      <c r="K43" s="245"/>
-      <c r="L43" s="245"/>
+      <c r="B43" s="237"/>
+      <c r="C43" s="237"/>
+      <c r="D43" s="237"/>
+      <c r="E43" s="237"/>
+      <c r="F43" s="237"/>
+      <c r="G43" s="237"/>
+      <c r="H43" s="237"/>
+      <c r="I43" s="237"/>
+      <c r="J43" s="237"/>
+      <c r="K43" s="237"/>
+      <c r="L43" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A42:L42"/>
-    <mergeCell ref="A43:L43"/>
-    <mergeCell ref="A35:L35"/>
-    <mergeCell ref="A36:L36"/>
-    <mergeCell ref="A37:L37"/>
-    <mergeCell ref="A38:L38"/>
-    <mergeCell ref="A39:L39"/>
-    <mergeCell ref="A40:L40"/>
     <mergeCell ref="A34:L34"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
@@ -13106,6 +13086,15 @@
     <mergeCell ref="A31:L31"/>
     <mergeCell ref="A32:L32"/>
     <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A42:L42"/>
+    <mergeCell ref="A43:L43"/>
+    <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A36:L36"/>
+    <mergeCell ref="A37:L37"/>
+    <mergeCell ref="A38:L38"/>
+    <mergeCell ref="A39:L39"/>
+    <mergeCell ref="A40:L40"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -13348,13 +13337,13 @@
         <v>125000</v>
       </c>
       <c r="J10" s="183" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K10" s="126">
         <v>147000</v>
       </c>
       <c r="L10" s="183" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="M10" s="124"/>
     </row>
